--- a/reports/latest/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/Excel/Automation_Test_Report.xlsx
@@ -3208,13 +3208,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>BUILD-87</t>
+    <t>BUILD-88</t>
   </si>
   <si>
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>9/12/2026, 2:42:53 AM</t>
+    <t>9/13/2026, 2:40:32 AM</t>
   </si>
   <si>
     <t>Target Device</t>
@@ -3793,7 +3793,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>361</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3813,7 +3813,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>405</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>945</v>
+        <v>739</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3853,7 +3853,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>568</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3873,7 +3873,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>351</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3893,7 +3893,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>441</v>
+        <v>855</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3913,7 +3913,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>365</v>
+        <v>937</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3933,7 +3933,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>377</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3953,7 +3953,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>382</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3973,7 +3973,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>948</v>
+        <v>842</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3993,7 +3993,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>698</v>
+        <v>747</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4013,7 +4013,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>677</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4033,7 +4033,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>563</v>
+        <v>868</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4053,7 +4053,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>946</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4073,7 +4073,7 @@
         <v>41</v>
       </c>
       <c r="F16">
-        <v>710</v>
+        <v>741</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4093,7 +4093,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>412</v>
+        <v>611</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4113,7 +4113,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>733</v>
+        <v>646</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4133,7 +4133,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>298</v>
+        <v>994</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4153,7 +4153,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>250</v>
+        <v>867</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4173,7 +4173,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>664</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4193,7 +4193,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>751</v>
+        <v>963</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4213,7 +4213,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>897</v>
+        <v>591</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4233,7 +4233,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>591</v>
+        <v>773</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4253,7 +4253,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>508</v>
+        <v>958</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4273,7 +4273,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>768</v>
+        <v>466</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4293,7 +4293,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>445</v>
+        <v>725</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>391</v>
+        <v>810</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4353,7 +4353,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>900</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4373,7 +4373,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>537</v>
+        <v>437</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4393,7 +4393,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>995</v>
+        <v>906</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4413,7 +4413,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>587</v>
+        <v>401</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4433,7 +4433,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>822</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>998</v>
+        <v>379</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4473,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>652</v>
+        <v>918</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4493,7 +4493,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>612</v>
+        <v>473</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4513,7 +4513,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>390</v>
+        <v>660</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4533,7 +4533,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>730</v>
+        <v>891</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4553,7 +4553,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>525</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4573,7 +4573,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>974</v>
+        <v>553</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4593,7 +4593,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>732</v>
+        <v>247</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4613,7 +4613,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>965</v>
+        <v>488</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,7 +4633,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>280</v>
+        <v>904</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4653,7 +4653,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>605</v>
+        <v>614</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4673,7 +4673,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>739</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4693,7 +4693,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>554</v>
+        <v>568</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4713,7 +4713,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>319</v>
+        <v>985</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4733,7 +4733,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>429</v>
+        <v>930</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4753,7 +4753,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>500</v>
+        <v>881</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>451</v>
+        <v>532</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4793,7 +4793,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>276</v>
+        <v>517</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4813,7 +4813,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>669</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4833,7 +4833,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>913</v>
+        <v>747</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>702</v>
+        <v>309</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4873,7 +4873,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>273</v>
+        <v>929</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>494</v>
+        <v>528</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4913,7 +4913,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>319</v>
+        <v>241</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4933,7 +4933,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>730</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4953,7 +4953,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>943</v>
+        <v>423</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4973,7 +4973,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>930</v>
+        <v>490</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4993,7 +4993,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>379</v>
+        <v>553</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -5013,7 +5013,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>448</v>
+        <v>969</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -5033,7 +5033,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>354</v>
+        <v>423</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -5053,7 +5053,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>735</v>
+        <v>793</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -5073,7 +5073,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>832</v>
+        <v>804</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -5093,7 +5093,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>758</v>
+        <v>952</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -5113,7 +5113,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>266</v>
+        <v>810</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5133,7 +5133,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>781</v>
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -5153,7 +5153,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>884</v>
+        <v>681</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -5173,7 +5173,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>757</v>
+        <v>661</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -5193,7 +5193,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>856</v>
+        <v>422</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -5213,7 +5213,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>629</v>
+        <v>930</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -5233,7 +5233,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>793</v>
+        <v>507</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -5253,7 +5253,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>200</v>
+        <v>596</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -5273,7 +5273,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>704</v>
+        <v>359</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5293,7 +5293,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>331</v>
+        <v>929</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5313,7 +5313,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>443</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5333,7 +5333,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>759</v>
+        <v>505</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5353,7 +5353,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>399</v>
+        <v>259</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5373,7 +5373,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>596</v>
+        <v>279</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5393,7 +5393,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>842</v>
+        <v>428</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5413,7 +5413,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>316</v>
+        <v>845</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5433,7 +5433,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>531</v>
+        <v>987</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5453,7 +5453,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>604</v>
+        <v>487</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5473,7 +5473,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>272</v>
+        <v>715</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5493,7 +5493,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>472</v>
+        <v>436</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5513,7 +5513,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>393</v>
+        <v>580</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5533,7 +5533,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>947</v>
+        <v>882</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5553,7 +5553,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>729</v>
+        <v>466</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -5573,7 +5573,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>412</v>
+        <v>985</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -5593,7 +5593,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>835</v>
+        <v>516</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5613,7 +5613,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>962</v>
+        <v>912</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5633,7 +5633,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>272</v>
+        <v>248</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>569</v>
+        <v>965</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>695</v>
+        <v>820</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5693,7 +5693,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>683</v>
+        <v>646</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -5713,7 +5713,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -5733,7 +5733,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>856</v>
+        <v>423</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -5753,7 +5753,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>366</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5773,7 +5773,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>954</v>
+        <v>997</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -5793,7 +5793,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>786</v>
+        <v>351</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -5813,7 +5813,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>222</v>
+        <v>551</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5833,7 +5833,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>211</v>
+        <v>559</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -5853,7 +5853,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>666</v>
+        <v>763</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -5873,7 +5873,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>979</v>
+        <v>201</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -5893,7 +5893,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>592</v>
+        <v>743</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -5913,7 +5913,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>741</v>
+        <v>822</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -5933,7 +5933,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>488</v>
+        <v>618</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -5953,7 +5953,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>488</v>
+        <v>809</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5973,7 +5973,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>550</v>
+        <v>418</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -5993,7 +5993,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>504</v>
+        <v>672</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -6013,7 +6013,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>251</v>
+        <v>724</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -6033,7 +6033,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>823</v>
+        <v>990</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -6053,7 +6053,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>996</v>
+        <v>755</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -6073,7 +6073,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>564</v>
+        <v>442</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -6093,7 +6093,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -6113,7 +6113,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>944</v>
+        <v>480</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -6133,7 +6133,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>805</v>
+        <v>893</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -6153,7 +6153,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>221</v>
+        <v>512</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -6173,7 +6173,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>800</v>
+        <v>923</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -6193,7 +6193,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>220</v>
+        <v>587</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -6213,7 +6213,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>363</v>
+        <v>743</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -6233,7 +6233,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>340</v>
+        <v>860</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -6253,7 +6253,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>362</v>
+        <v>278</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -6273,7 +6273,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>411</v>
+        <v>904</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6293,7 +6293,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>290</v>
+        <v>794</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6313,7 +6313,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>269</v>
+        <v>928</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6333,7 +6333,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>220</v>
+        <v>408</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6353,7 +6353,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>388</v>
+        <v>412</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6373,7 +6373,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>721</v>
+        <v>860</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6393,7 +6393,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>716</v>
+        <v>304</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6413,7 +6413,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>603</v>
+        <v>876</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -6433,7 +6433,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>209</v>
+        <v>273</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -6453,7 +6453,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>451</v>
+        <v>682</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6473,7 +6473,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>511</v>
+        <v>698</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6493,7 +6493,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>391</v>
+        <v>745</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6513,7 +6513,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>991</v>
+        <v>365</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -6533,7 +6533,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>297</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>844</v>
+        <v>927</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6573,7 +6573,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>472</v>
+        <v>666</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6593,7 +6593,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>762</v>
+        <v>324</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -6613,7 +6613,7 @@
         <v>41</v>
       </c>
       <c r="F143">
-        <v>422</v>
+        <v>980</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -6633,7 +6633,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -6653,7 +6653,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>386</v>
+        <v>803</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>951</v>
+        <v>968</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -6693,7 +6693,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>538</v>
+        <v>833</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -6713,7 +6713,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>529</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -6733,7 +6733,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>224</v>
+        <v>500</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6753,7 +6753,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>339</v>
+        <v>607</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -6773,7 +6773,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>743</v>
+        <v>257</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -6793,7 +6793,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>725</v>
+        <v>773</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6813,7 +6813,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>499</v>
+        <v>730</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -6833,7 +6833,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>573</v>
+        <v>530</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -6853,7 +6853,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>610</v>
+        <v>767</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -6873,7 +6873,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>750</v>
+        <v>531</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>232</v>
+        <v>443</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6913,7 +6913,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>397</v>
+        <v>548</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -6933,7 +6933,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>305</v>
+        <v>744</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -6953,7 +6953,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>511</v>
+        <v>463</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -6973,7 +6973,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>205</v>
+        <v>346</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -6993,7 +6993,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>744</v>
+        <v>678</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -7013,7 +7013,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>962</v>
+        <v>769</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -7033,7 +7033,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>548</v>
+        <v>928</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -7053,7 +7053,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -7073,7 +7073,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>395</v>
+        <v>883</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -7093,7 +7093,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>288</v>
+        <v>487</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -7113,7 +7113,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>640</v>
+        <v>609</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -7133,7 +7133,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>294</v>
+        <v>745</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -7153,7 +7153,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>510</v>
+        <v>666</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -7173,7 +7173,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>454</v>
+        <v>408</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -7193,7 +7193,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>302</v>
+        <v>890</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -7213,7 +7213,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>515</v>
+        <v>798</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>862</v>
+        <v>815</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -7253,7 +7253,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>483</v>
+        <v>868</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -7273,7 +7273,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>854</v>
+        <v>645</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7293,7 +7293,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>553</v>
+        <v>840</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7313,7 +7313,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>733</v>
+        <v>540</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7333,7 +7333,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>981</v>
+        <v>739</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7353,7 +7353,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>952</v>
+        <v>253</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7373,7 +7373,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>568</v>
+        <v>315</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7393,7 +7393,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>774</v>
+        <v>520</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7413,7 +7413,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>799</v>
+        <v>773</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7433,7 +7433,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>762</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -7453,7 +7453,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>360</v>
+        <v>823</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -7473,7 +7473,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>701</v>
+        <v>390</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>449</v>
+        <v>467</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -7513,7 +7513,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>640</v>
+        <v>214</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7533,7 +7533,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>719</v>
+        <v>704</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -7553,7 +7553,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>765</v>
+        <v>439</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>779</v>
+        <v>708</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -7593,7 +7593,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -7613,7 +7613,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>700</v>
+        <v>320</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -7633,7 +7633,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>471</v>
+        <v>809</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -7653,7 +7653,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>366</v>
+        <v>526</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -7673,7 +7673,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>232</v>
+        <v>587</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -7693,7 +7693,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>803</v>
+        <v>760</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -7713,7 +7713,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>504</v>
+        <v>400</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -7733,7 +7733,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>954</v>
+        <v>265</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -7753,7 +7753,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>779</v>
+        <v>263</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -7773,7 +7773,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>839</v>
+        <v>213</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -7793,7 +7793,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>656</v>
+        <v>398</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -7813,7 +7813,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>415</v>
+        <v>331</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -7833,7 +7833,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>276</v>
+        <v>574</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7853,7 +7853,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>810</v>
+        <v>323</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7873,7 +7873,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>960</v>
+        <v>995</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -7893,7 +7893,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>253</v>
+        <v>296</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -7913,7 +7913,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>561</v>
+        <v>748</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -7933,7 +7933,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>800</v>
+        <v>929</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -7953,7 +7953,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>634</v>
+        <v>280</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -7973,7 +7973,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>561</v>
+        <v>805</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7993,7 +7993,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>391</v>
+        <v>761</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -8013,7 +8013,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>654</v>
+        <v>919</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -8033,7 +8033,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>920</v>
+        <v>943</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -8053,7 +8053,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>758</v>
+        <v>892</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -8073,7 +8073,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>872</v>
+        <v>246</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -8093,7 +8093,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>560</v>
+        <v>400</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -8113,7 +8113,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>310</v>
+        <v>839</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -8133,7 +8133,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>322</v>
+        <v>298</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -8153,7 +8153,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>745</v>
+        <v>318</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -8173,7 +8173,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>722</v>
+        <v>361</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -8193,7 +8193,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>719</v>
+        <v>212</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -8213,7 +8213,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>441</v>
+        <v>772</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -8233,7 +8233,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>560</v>
+        <v>774</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -8253,7 +8253,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>312</v>
+        <v>503</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8273,7 +8273,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>455</v>
+        <v>902</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8293,7 +8293,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>946</v>
+        <v>366</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8313,7 +8313,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>826</v>
+        <v>213</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8333,7 +8333,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>509</v>
+        <v>992</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -8353,7 +8353,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>776</v>
+        <v>784</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8373,7 +8373,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>238</v>
+        <v>907</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8393,7 +8393,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>656</v>
+        <v>449</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8433,7 +8433,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>681</v>
+        <v>795</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -8453,7 +8453,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>378</v>
+        <v>303</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -8473,7 +8473,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>914</v>
+        <v>791</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -8493,7 +8493,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>393</v>
+        <v>779</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -8513,7 +8513,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>668</v>
+        <v>971</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -8533,7 +8533,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>334</v>
+        <v>935</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -8553,7 +8553,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>698</v>
+        <v>637</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8573,7 +8573,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>786</v>
+        <v>215</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -8593,7 +8593,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>231</v>
+        <v>477</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -8613,7 +8613,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>843</v>
+        <v>429</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -8633,7 +8633,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8653,7 +8653,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>231</v>
+        <v>827</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8673,7 +8673,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>218</v>
+        <v>498</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -8693,7 +8693,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>325</v>
+        <v>500</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -8713,7 +8713,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>824</v>
+        <v>728</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8733,7 +8733,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>296</v>
+        <v>496</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -8753,7 +8753,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>787</v>
+        <v>596</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8773,7 +8773,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>450</v>
+        <v>554</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8793,7 +8793,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>854</v>
+        <v>994</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8813,7 +8813,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>550</v>
+        <v>476</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -8833,7 +8833,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>785</v>
+        <v>557</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -8853,7 +8853,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>229</v>
+        <v>254</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>528</v>
+        <v>660</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -8893,7 +8893,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>634</v>
+        <v>476</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -8913,7 +8913,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>633</v>
+        <v>587</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -8933,7 +8933,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>885</v>
+        <v>731</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -8953,7 +8953,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>627</v>
+        <v>683</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -8973,7 +8973,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>858</v>
+        <v>657</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -8993,7 +8993,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>275</v>
+        <v>668</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -9013,7 +9013,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -9033,7 +9033,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>449</v>
+        <v>610</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -9053,7 +9053,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>672</v>
+        <v>614</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -9073,7 +9073,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>937</v>
+        <v>588</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -9093,7 +9093,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>286</v>
+        <v>992</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -9113,7 +9113,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>269</v>
+        <v>558</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -9133,7 +9133,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>969</v>
+        <v>738</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -9153,7 +9153,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>566</v>
+        <v>657</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -9173,7 +9173,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>913</v>
+        <v>730</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -9193,7 +9193,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>232</v>
+        <v>675</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -9213,7 +9213,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>459</v>
+        <v>644</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -9233,7 +9233,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>535</v>
+        <v>434</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -9253,7 +9253,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>850</v>
+        <v>401</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -9273,7 +9273,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>930</v>
+        <v>715</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -9293,7 +9293,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>482</v>
+        <v>664</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -9313,7 +9313,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>582</v>
+        <v>491</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -9333,7 +9333,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>282</v>
+        <v>992</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -9353,7 +9353,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>662</v>
+        <v>609</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -9373,7 +9373,7 @@
         <v>41</v>
       </c>
       <c r="F281">
-        <v>634</v>
+        <v>430</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -9393,7 +9393,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>913</v>
+        <v>571</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -9413,7 +9413,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>849</v>
+        <v>615</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -9433,7 +9433,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>943</v>
+        <v>974</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -9453,7 +9453,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>903</v>
+        <v>641</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -9473,7 +9473,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>793</v>
+        <v>883</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -9493,7 +9493,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>485</v>
+        <v>594</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -9513,7 +9513,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>593</v>
+        <v>340</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -9533,7 +9533,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>353</v>
+        <v>619</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -9553,7 +9553,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>716</v>
+        <v>702</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -9573,7 +9573,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>300</v>
+        <v>914</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -9593,7 +9593,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>684</v>
+        <v>596</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -9613,7 +9613,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>492</v>
+        <v>675</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -9633,7 +9633,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>811</v>
+        <v>727</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -9653,7 +9653,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>959</v>
+        <v>253</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -9673,7 +9673,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>318</v>
+        <v>656</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -9693,7 +9693,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>821</v>
+        <v>572</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -9713,7 +9713,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>769</v>
+        <v>902</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -9733,7 +9733,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>376</v>
+        <v>447</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -9753,7 +9753,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>434</v>
+        <v>484</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -9773,7 +9773,7 @@
         <v>622</v>
       </c>
       <c r="F301">
-        <v>562</v>
+        <v>527</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -9793,7 +9793,7 @@
         <v>622</v>
       </c>
       <c r="F302">
-        <v>718</v>
+        <v>459</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -9813,7 +9813,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>389</v>
+        <v>971</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -9833,7 +9833,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>739</v>
+        <v>912</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -9853,7 +9853,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>287</v>
+        <v>312</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -9873,7 +9873,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>521</v>
+        <v>414</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -9893,7 +9893,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>426</v>
+        <v>894</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -9913,7 +9913,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>976</v>
+        <v>776</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -9933,7 +9933,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>675</v>
+        <v>839</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>715</v>
+        <v>655</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -9973,7 +9973,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>565</v>
+        <v>646</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -9993,7 +9993,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>389</v>
+        <v>284</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -10013,7 +10013,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>613</v>
+        <v>399</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -10033,7 +10033,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>619</v>
+        <v>323</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -10053,7 +10053,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>575</v>
+        <v>284</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -10073,7 +10073,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>466</v>
+        <v>944</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -10093,7 +10093,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>952</v>
+        <v>798</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -10113,7 +10113,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>857</v>
+        <v>691</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -10133,7 +10133,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>320</v>
+        <v>857</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>274</v>
+        <v>429</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -10173,7 +10173,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>221</v>
+        <v>387</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -10193,7 +10193,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>840</v>
+        <v>466</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -10213,7 +10213,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>655</v>
+        <v>824</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -10233,7 +10233,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>884</v>
+        <v>303</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -10253,7 +10253,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>481</v>
+        <v>320</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -10273,7 +10273,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>435</v>
+        <v>613</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -10293,7 +10293,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>959</v>
+        <v>954</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -10313,7 +10313,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>294</v>
+        <v>830</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -10333,7 +10333,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>761</v>
+        <v>449</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -10353,7 +10353,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>416</v>
+        <v>929</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -10373,7 +10373,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>907</v>
+        <v>393</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -10393,7 +10393,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>521</v>
+        <v>810</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -10413,7 +10413,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>273</v>
+        <v>721</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -10433,7 +10433,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>698</v>
+        <v>231</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -10453,7 +10453,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>250</v>
+        <v>354</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -10473,7 +10473,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>253</v>
+        <v>293</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -10493,7 +10493,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>500</v>
+        <v>479</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -10513,7 +10513,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>425</v>
+        <v>935</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -10533,7 +10533,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>781</v>
+        <v>415</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -10553,7 +10553,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>381</v>
+        <v>892</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -10573,7 +10573,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>700</v>
+        <v>961</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -10593,7 +10593,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>435</v>
+        <v>819</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -10613,7 +10613,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>700</v>
+        <v>981</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -10633,7 +10633,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>611</v>
+        <v>444</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -10653,7 +10653,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>967</v>
+        <v>227</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -10673,7 +10673,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>779</v>
+        <v>570</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -10693,7 +10693,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>492</v>
+        <v>734</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -10713,7 +10713,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>414</v>
+        <v>299</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -10733,7 +10733,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>554</v>
+        <v>303</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -10753,7 +10753,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>201</v>
+        <v>862</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -10773,7 +10773,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>308</v>
+        <v>903</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -10793,7 +10793,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>890</v>
+        <v>901</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -10813,7 +10813,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>619</v>
+        <v>307</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -10833,7 +10833,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>365</v>
+        <v>723</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -10853,7 +10853,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>402</v>
+        <v>308</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -10873,7 +10873,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>300</v>
+        <v>524</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -10893,7 +10893,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>224</v>
+        <v>797</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -10913,7 +10913,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>884</v>
+        <v>689</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -10933,7 +10933,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>289</v>
+        <v>555</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -10953,7 +10953,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>877</v>
+        <v>577</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -10973,7 +10973,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>209</v>
+        <v>738</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -10993,7 +10993,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>312</v>
+        <v>498</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -11013,7 +11013,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>966</v>
+        <v>505</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -11033,7 +11033,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>649</v>
+        <v>632</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -11053,7 +11053,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>881</v>
+        <v>661</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -11073,7 +11073,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>705</v>
+        <v>371</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -11093,7 +11093,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>864</v>
+        <v>568</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -11113,7 +11113,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>567</v>
+        <v>681</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -11133,7 +11133,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>521</v>
+        <v>878</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -11153,7 +11153,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>513</v>
+        <v>274</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -11173,7 +11173,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>905</v>
+        <v>247</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -11193,7 +11193,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>520</v>
+        <v>795</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -11213,7 +11213,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>232</v>
+        <v>207</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -11233,7 +11233,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>208</v>
+        <v>896</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -11253,7 +11253,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>702</v>
+        <v>270</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -11273,7 +11273,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>952</v>
+        <v>748</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -11293,7 +11293,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>741</v>
+        <v>369</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>521</v>
+        <v>411</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -11333,7 +11333,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>923</v>
+        <v>856</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -11353,7 +11353,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>843</v>
+        <v>513</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -11373,7 +11373,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>534</v>
+        <v>341</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -11393,7 +11393,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>779</v>
+        <v>268</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -11413,7 +11413,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>978</v>
+        <v>690</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -11433,7 +11433,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>268</v>
+        <v>840</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -11453,7 +11453,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>377</v>
+        <v>318</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -11473,7 +11473,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>856</v>
+        <v>598</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -11493,7 +11493,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>348</v>
+        <v>541</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -11513,7 +11513,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>804</v>
+        <v>543</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -11533,7 +11533,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>930</v>
+        <v>260</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -11553,7 +11553,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>544</v>
+        <v>292</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -11573,7 +11573,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>392</v>
+        <v>693</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -11593,7 +11593,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -11613,7 +11613,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>248</v>
+        <v>649</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -11633,7 +11633,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>832</v>
+        <v>719</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -11653,7 +11653,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>487</v>
+        <v>975</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -11673,7 +11673,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>765</v>
+        <v>926</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -11693,7 +11693,7 @@
         <v>10</v>
       </c>
       <c r="F397">
-        <v>623</v>
+        <v>698</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -11713,7 +11713,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>764</v>
+        <v>459</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -11733,7 +11733,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>488</v>
+        <v>849</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -11753,7 +11753,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>207</v>
+        <v>321</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -11773,7 +11773,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>858</v>
+        <v>532</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -11793,7 +11793,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>655</v>
+        <v>476</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -11813,7 +11813,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>232</v>
+        <v>718</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -11833,7 +11833,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>625</v>
+        <v>873</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>767</v>
+        <v>916</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -11873,7 +11873,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>395</v>
+        <v>715</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -11893,7 +11893,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>623</v>
+        <v>233</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -11913,7 +11913,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>504</v>
+        <v>965</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -11933,7 +11933,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>549</v>
+        <v>227</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -11953,7 +11953,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>669</v>
+        <v>539</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -11973,7 +11973,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>211</v>
+        <v>397</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -11993,7 +11993,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>311</v>
+        <v>270</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -12013,7 +12013,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>832</v>
+        <v>821</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -12033,7 +12033,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>377</v>
+        <v>935</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -12053,7 +12053,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>335</v>
+        <v>857</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -12073,7 +12073,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>697</v>
+        <v>335</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -12093,7 +12093,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>820</v>
+        <v>904</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -12113,7 +12113,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>527</v>
+        <v>595</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -12133,7 +12133,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>809</v>
+        <v>304</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -12153,7 +12153,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>713</v>
+        <v>468</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -12173,7 +12173,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>315</v>
+        <v>509</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -12193,7 +12193,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>940</v>
+        <v>603</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -12213,7 +12213,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>225</v>
+        <v>510</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -12233,7 +12233,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>578</v>
+        <v>426</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -12253,7 +12253,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>934</v>
+        <v>659</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -12273,7 +12273,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>235</v>
+        <v>554</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -12293,7 +12293,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>456</v>
+        <v>507</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -12313,7 +12313,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>906</v>
+        <v>558</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>800</v>
+        <v>213</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -12353,7 +12353,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>789</v>
+        <v>816</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -12373,7 +12373,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>291</v>
+        <v>338</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -12393,7 +12393,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>222</v>
+        <v>834</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -12413,7 +12413,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>927</v>
+        <v>254</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -12433,7 +12433,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>923</v>
+        <v>680</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -12453,7 +12453,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>703</v>
+        <v>616</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -12473,7 +12473,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>856</v>
+        <v>816</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -12493,7 +12493,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>344</v>
+        <v>860</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -12513,7 +12513,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>927</v>
+        <v>307</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12533,7 +12533,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>342</v>
+        <v>953</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12553,7 +12553,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>698</v>
+        <v>792</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12573,7 +12573,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>362</v>
+        <v>936</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12593,7 +12593,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>668</v>
+        <v>789</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -12613,7 +12613,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>892</v>
+        <v>908</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12633,7 +12633,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>493</v>
+        <v>685</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -12653,7 +12653,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>731</v>
+        <v>326</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -12673,7 +12673,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>360</v>
+        <v>211</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -12693,7 +12693,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>421</v>
+        <v>867</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12713,7 +12713,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>829</v>
+        <v>274</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12733,7 +12733,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>268</v>
+        <v>408</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -12753,7 +12753,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>928</v>
+        <v>344</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -12773,7 +12773,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>853</v>
+        <v>969</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -12793,7 +12793,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>938</v>
+        <v>722</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -12813,7 +12813,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>576</v>
+        <v>599</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -12833,7 +12833,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>575</v>
+        <v>588</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -12853,7 +12853,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>525</v>
+        <v>418</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -12873,7 +12873,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>812</v>
+        <v>708</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -12893,7 +12893,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>503</v>
+        <v>314</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -12913,7 +12913,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>854</v>
+        <v>438</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -12933,7 +12933,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>999</v>
+        <v>441</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -12953,7 +12953,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>321</v>
+        <v>333</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -12973,7 +12973,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>820</v>
+        <v>317</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -12993,7 +12993,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>802</v>
+        <v>947</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -13013,7 +13013,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>725</v>
+        <v>876</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -13033,7 +13033,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -13053,7 +13053,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>242</v>
+        <v>529</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -13073,7 +13073,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>676</v>
+        <v>480</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -13093,7 +13093,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>978</v>
+        <v>408</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -13113,7 +13113,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>571</v>
+        <v>885</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -13133,7 +13133,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>246</v>
+        <v>382</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -13153,7 +13153,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>942</v>
+        <v>266</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -13173,7 +13173,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>598</v>
+        <v>527</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -13193,7 +13193,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -13213,7 +13213,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>266</v>
+        <v>648</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -13233,7 +13233,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>296</v>
+        <v>637</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -13253,7 +13253,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>501</v>
+        <v>327</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -13273,7 +13273,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>931</v>
+        <v>777</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -13293,7 +13293,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>613</v>
+        <v>348</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -13313,7 +13313,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>367</v>
+        <v>852</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -13333,7 +13333,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -13353,7 +13353,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>250</v>
+        <v>572</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -13373,7 +13373,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>803</v>
+        <v>936</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -13393,7 +13393,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>413</v>
+        <v>648</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -13413,7 +13413,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>890</v>
+        <v>996</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -13433,7 +13433,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>721</v>
+        <v>418</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -13453,7 +13453,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>354</v>
+        <v>877</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -13473,7 +13473,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>516</v>
+        <v>283</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -13493,7 +13493,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>587</v>
+        <v>559</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -13513,7 +13513,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>799</v>
+        <v>882</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -13533,7 +13533,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>805</v>
+        <v>579</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -13553,7 +13553,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>990</v>
+        <v>879</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -13573,7 +13573,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>952</v>
+        <v>899</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -13593,7 +13593,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>445</v>
+        <v>926</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -13613,7 +13613,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>713</v>
+        <v>724</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -13633,7 +13633,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>722</v>
+        <v>898</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -13653,7 +13653,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>695</v>
+        <v>653</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13673,7 +13673,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>229</v>
+        <v>292</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -13693,7 +13693,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>327</v>
+        <v>440</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13713,7 +13713,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>975</v>
+        <v>754</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -13733,7 +13733,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>304</v>
+        <v>998</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -13753,7 +13753,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>662</v>
+        <v>743</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -13773,7 +13773,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>498</v>
+        <v>431</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -13793,7 +13793,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>529</v>
+        <v>818</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -13813,7 +13813,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>652</v>
+        <v>580</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -13833,7 +13833,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>657</v>
+        <v>364</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -13853,7 +13853,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>453</v>
+        <v>287</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -13873,7 +13873,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>299</v>
+        <v>418</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -13893,7 +13893,7 @@
         <v>10</v>
       </c>
       <c r="F507">
-        <v>859</v>
+        <v>238</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -13913,7 +13913,7 @@
         <v>10</v>
       </c>
       <c r="F508">
-        <v>849</v>
+        <v>405</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -13933,7 +13933,7 @@
         <v>10</v>
       </c>
       <c r="F509">
-        <v>969</v>
+        <v>760</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -13953,7 +13953,7 @@
         <v>10</v>
       </c>
       <c r="F510">
-        <v>268</v>
+        <v>405</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -13973,7 +13973,7 @@
         <v>10</v>
       </c>
       <c r="F511">
-        <v>244</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -14034,7 +14034,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>361</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -14054,7 +14054,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>405</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -14074,7 +14074,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>945</v>
+        <v>739</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -14094,7 +14094,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>568</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -14114,7 +14114,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>351</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -14134,7 +14134,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>441</v>
+        <v>855</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -14154,7 +14154,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>365</v>
+        <v>937</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -14174,7 +14174,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>377</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -14194,7 +14194,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>382</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -14214,7 +14214,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>948</v>
+        <v>842</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -14234,7 +14234,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>698</v>
+        <v>747</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -14254,7 +14254,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>677</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -14274,7 +14274,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>563</v>
+        <v>868</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -14294,7 +14294,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>946</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -14314,7 +14314,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>412</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -14334,7 +14334,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>733</v>
+        <v>646</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -14354,7 +14354,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>298</v>
+        <v>994</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -14374,7 +14374,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>250</v>
+        <v>867</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -14394,7 +14394,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>664</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -14414,7 +14414,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>751</v>
+        <v>963</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -14434,7 +14434,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>897</v>
+        <v>591</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -14454,7 +14454,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>591</v>
+        <v>773</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -14474,7 +14474,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>508</v>
+        <v>958</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -14494,7 +14494,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>768</v>
+        <v>466</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -14514,7 +14514,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>445</v>
+        <v>725</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -14534,7 +14534,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>391</v>
+        <v>810</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -14554,7 +14554,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -14574,7 +14574,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -14594,7 +14594,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>537</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -14614,7 +14614,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>995</v>
+        <v>906</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -14634,7 +14634,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>587</v>
+        <v>401</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -14654,7 +14654,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>822</v>
+        <v>369</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -14674,7 +14674,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>998</v>
+        <v>379</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -14694,7 +14694,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>652</v>
+        <v>918</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -14714,7 +14714,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>612</v>
+        <v>473</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -14734,7 +14734,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>390</v>
+        <v>660</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -14754,7 +14754,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>730</v>
+        <v>891</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -14774,7 +14774,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>525</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -14794,7 +14794,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>974</v>
+        <v>553</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -14814,7 +14814,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>732</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -14834,7 +14834,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>965</v>
+        <v>488</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -14854,7 +14854,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>280</v>
+        <v>904</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -14874,7 +14874,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>605</v>
+        <v>614</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -14894,7 +14894,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>739</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -14914,7 +14914,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>554</v>
+        <v>568</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -14934,7 +14934,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>319</v>
+        <v>985</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -14954,7 +14954,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>429</v>
+        <v>930</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -14974,7 +14974,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>500</v>
+        <v>881</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -14994,7 +14994,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>451</v>
+        <v>532</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -15014,7 +15014,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>276</v>
+        <v>517</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -15034,7 +15034,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>669</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -15054,7 +15054,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>913</v>
+        <v>747</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -15074,7 +15074,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>702</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -15094,7 +15094,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>273</v>
+        <v>929</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -15114,7 +15114,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>494</v>
+        <v>528</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -15134,7 +15134,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>319</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -15154,7 +15154,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>730</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -15174,7 +15174,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>943</v>
+        <v>423</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -15194,7 +15194,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>930</v>
+        <v>490</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -15214,7 +15214,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>379</v>
+        <v>553</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -15234,7 +15234,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>448</v>
+        <v>969</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -15254,7 +15254,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>354</v>
+        <v>423</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -15274,7 +15274,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>735</v>
+        <v>793</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -15294,7 +15294,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>832</v>
+        <v>804</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -15314,7 +15314,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>758</v>
+        <v>952</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -15334,7 +15334,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>266</v>
+        <v>810</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -15354,7 +15354,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>781</v>
+        <v>351</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -15374,7 +15374,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>884</v>
+        <v>681</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -15394,7 +15394,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>757</v>
+        <v>661</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -15414,7 +15414,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>856</v>
+        <v>422</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -15434,7 +15434,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>629</v>
+        <v>930</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -15454,7 +15454,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>793</v>
+        <v>507</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -15474,7 +15474,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>200</v>
+        <v>596</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -15494,7 +15494,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>704</v>
+        <v>359</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -15514,7 +15514,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>331</v>
+        <v>929</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -15534,7 +15534,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>443</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -15554,7 +15554,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>759</v>
+        <v>505</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -15574,7 +15574,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>399</v>
+        <v>259</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -15594,7 +15594,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>596</v>
+        <v>279</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -15614,7 +15614,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>842</v>
+        <v>428</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -15634,7 +15634,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>316</v>
+        <v>845</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -15654,7 +15654,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>531</v>
+        <v>987</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -15674,7 +15674,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>604</v>
+        <v>487</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -15694,7 +15694,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>272</v>
+        <v>715</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -15714,7 +15714,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>472</v>
+        <v>436</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -15734,7 +15734,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>393</v>
+        <v>580</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -15754,7 +15754,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>947</v>
+        <v>882</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -15774,7 +15774,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>729</v>
+        <v>466</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -15794,7 +15794,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>412</v>
+        <v>985</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -15814,7 +15814,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>835</v>
+        <v>516</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -15834,7 +15834,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>962</v>
+        <v>912</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -15854,7 +15854,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>272</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -15874,7 +15874,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>569</v>
+        <v>965</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -15894,7 +15894,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>695</v>
+        <v>820</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -15914,7 +15914,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>683</v>
+        <v>646</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -15934,7 +15934,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>563</v>
+        <v>591</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -15954,7 +15954,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>856</v>
+        <v>423</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -15974,7 +15974,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>366</v>
+        <v>228</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -15994,7 +15994,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>954</v>
+        <v>997</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -16014,7 +16014,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>786</v>
+        <v>351</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -16034,7 +16034,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>222</v>
+        <v>551</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -16054,7 +16054,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>211</v>
+        <v>559</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -16074,7 +16074,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>666</v>
+        <v>763</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -16094,7 +16094,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>979</v>
+        <v>201</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -16114,7 +16114,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>592</v>
+        <v>743</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -16134,7 +16134,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>741</v>
+        <v>822</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -16154,7 +16154,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>488</v>
+        <v>618</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -16174,7 +16174,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>488</v>
+        <v>809</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -16194,7 +16194,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>550</v>
+        <v>418</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -16214,7 +16214,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>504</v>
+        <v>672</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -16234,7 +16234,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>251</v>
+        <v>724</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -16254,7 +16254,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>823</v>
+        <v>990</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -16274,7 +16274,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>996</v>
+        <v>755</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -16294,7 +16294,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>564</v>
+        <v>442</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -16314,7 +16314,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>473</v>
+        <v>421</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -16334,7 +16334,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>944</v>
+        <v>480</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -16354,7 +16354,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>805</v>
+        <v>893</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -16374,7 +16374,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>221</v>
+        <v>512</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -16394,7 +16394,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>800</v>
+        <v>923</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -16414,7 +16414,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>220</v>
+        <v>587</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -16434,7 +16434,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>363</v>
+        <v>743</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -16454,7 +16454,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>340</v>
+        <v>860</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -16474,7 +16474,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>362</v>
+        <v>278</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -16494,7 +16494,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>411</v>
+        <v>904</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -16514,7 +16514,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>290</v>
+        <v>794</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -16534,7 +16534,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>269</v>
+        <v>928</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -16554,7 +16554,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>220</v>
+        <v>408</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -16574,7 +16574,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>388</v>
+        <v>412</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -16594,7 +16594,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>721</v>
+        <v>860</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -16614,7 +16614,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>716</v>
+        <v>304</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -16634,7 +16634,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>603</v>
+        <v>876</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -16654,7 +16654,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>209</v>
+        <v>273</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -16674,7 +16674,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>451</v>
+        <v>682</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -16694,7 +16694,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>511</v>
+        <v>698</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -16714,7 +16714,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>391</v>
+        <v>745</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -16734,7 +16734,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>991</v>
+        <v>365</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -16754,7 +16754,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>297</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -16774,7 +16774,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>844</v>
+        <v>927</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -16794,7 +16794,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>472</v>
+        <v>666</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -16814,7 +16814,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>762</v>
+        <v>324</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -16834,7 +16834,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -16854,7 +16854,7 @@
         <v>10</v>
       </c>
       <c r="F143">
-        <v>386</v>
+        <v>803</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -16874,7 +16874,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>951</v>
+        <v>968</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -16894,7 +16894,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>538</v>
+        <v>833</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -16914,7 +16914,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>529</v>
+        <v>415</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -16934,7 +16934,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>224</v>
+        <v>500</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -16954,7 +16954,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>339</v>
+        <v>607</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -16974,7 +16974,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>743</v>
+        <v>257</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -16994,7 +16994,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>725</v>
+        <v>773</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -17014,7 +17014,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>499</v>
+        <v>730</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -17034,7 +17034,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>573</v>
+        <v>530</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -17054,7 +17054,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>610</v>
+        <v>767</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -17074,7 +17074,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>750</v>
+        <v>531</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -17094,7 +17094,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>232</v>
+        <v>443</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -17114,7 +17114,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>397</v>
+        <v>548</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -17134,7 +17134,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>305</v>
+        <v>744</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -17154,7 +17154,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>511</v>
+        <v>463</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -17174,7 +17174,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>205</v>
+        <v>346</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -17194,7 +17194,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>744</v>
+        <v>678</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -17214,7 +17214,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>962</v>
+        <v>769</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -17234,7 +17234,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>548</v>
+        <v>928</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -17254,7 +17254,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -17274,7 +17274,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>395</v>
+        <v>883</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -17294,7 +17294,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>288</v>
+        <v>487</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -17314,7 +17314,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>640</v>
+        <v>609</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -17334,7 +17334,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>294</v>
+        <v>745</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -17354,7 +17354,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>510</v>
+        <v>666</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -17374,7 +17374,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>454</v>
+        <v>408</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -17394,7 +17394,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>302</v>
+        <v>890</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -17414,7 +17414,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>515</v>
+        <v>798</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -17434,7 +17434,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>862</v>
+        <v>815</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -17454,7 +17454,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>483</v>
+        <v>868</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -17474,7 +17474,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>854</v>
+        <v>645</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -17494,7 +17494,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>553</v>
+        <v>840</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -17514,7 +17514,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>733</v>
+        <v>540</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -17534,7 +17534,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>981</v>
+        <v>739</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -17554,7 +17554,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>952</v>
+        <v>253</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -17574,7 +17574,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>568</v>
+        <v>315</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -17594,7 +17594,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>774</v>
+        <v>520</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -17614,7 +17614,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>799</v>
+        <v>773</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -17634,7 +17634,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>762</v>
+        <v>453</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -17654,7 +17654,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>360</v>
+        <v>823</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -17674,7 +17674,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>701</v>
+        <v>390</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -17694,7 +17694,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>449</v>
+        <v>467</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -17714,7 +17714,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>640</v>
+        <v>214</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -17734,7 +17734,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>719</v>
+        <v>704</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -17754,7 +17754,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>765</v>
+        <v>439</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -17774,7 +17774,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>779</v>
+        <v>708</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -17794,7 +17794,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -17814,7 +17814,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>700</v>
+        <v>320</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -17834,7 +17834,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>471</v>
+        <v>809</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -17854,7 +17854,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>366</v>
+        <v>526</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -17874,7 +17874,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>232</v>
+        <v>587</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -17894,7 +17894,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>803</v>
+        <v>760</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -17914,7 +17914,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>504</v>
+        <v>400</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -17934,7 +17934,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>954</v>
+        <v>265</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -17954,7 +17954,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>779</v>
+        <v>263</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -17974,7 +17974,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>839</v>
+        <v>213</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -17994,7 +17994,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>656</v>
+        <v>398</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -18014,7 +18014,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>415</v>
+        <v>331</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -18034,7 +18034,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>276</v>
+        <v>574</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -18054,7 +18054,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>810</v>
+        <v>323</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -18074,7 +18074,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>960</v>
+        <v>995</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -18094,7 +18094,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>253</v>
+        <v>296</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -18114,7 +18114,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>561</v>
+        <v>748</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -18134,7 +18134,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>800</v>
+        <v>929</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -18154,7 +18154,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>634</v>
+        <v>280</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -18174,7 +18174,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>561</v>
+        <v>805</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -18194,7 +18194,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>391</v>
+        <v>761</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -18214,7 +18214,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>654</v>
+        <v>919</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -18234,7 +18234,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>920</v>
+        <v>943</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -18254,7 +18254,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>758</v>
+        <v>892</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -18274,7 +18274,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>872</v>
+        <v>246</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -18294,7 +18294,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>560</v>
+        <v>400</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -18314,7 +18314,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>310</v>
+        <v>839</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -18334,7 +18334,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>322</v>
+        <v>298</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -18354,7 +18354,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>745</v>
+        <v>318</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -18374,7 +18374,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>722</v>
+        <v>361</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -18394,7 +18394,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>719</v>
+        <v>212</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -18414,7 +18414,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>441</v>
+        <v>772</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -18434,7 +18434,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>560</v>
+        <v>774</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -18454,7 +18454,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>312</v>
+        <v>503</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -18474,7 +18474,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>455</v>
+        <v>902</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -18494,7 +18494,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>946</v>
+        <v>366</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -18514,7 +18514,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>826</v>
+        <v>213</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -18534,7 +18534,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>509</v>
+        <v>992</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -18554,7 +18554,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>776</v>
+        <v>784</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -18574,7 +18574,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>238</v>
+        <v>907</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -18594,7 +18594,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -18614,7 +18614,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>656</v>
+        <v>449</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -18634,7 +18634,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>681</v>
+        <v>795</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -18654,7 +18654,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>378</v>
+        <v>303</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -18674,7 +18674,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>914</v>
+        <v>791</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -18694,7 +18694,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>393</v>
+        <v>779</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -18714,7 +18714,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>668</v>
+        <v>971</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -18734,7 +18734,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>334</v>
+        <v>935</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -18754,7 +18754,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>698</v>
+        <v>637</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -18774,7 +18774,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>786</v>
+        <v>215</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -18794,7 +18794,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>231</v>
+        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -18814,7 +18814,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>843</v>
+        <v>429</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -18834,7 +18834,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -18854,7 +18854,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>231</v>
+        <v>827</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -18874,7 +18874,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>218</v>
+        <v>498</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -18894,7 +18894,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>325</v>
+        <v>500</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -18914,7 +18914,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>824</v>
+        <v>728</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -18934,7 +18934,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>296</v>
+        <v>496</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -18954,7 +18954,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>787</v>
+        <v>596</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -18974,7 +18974,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>450</v>
+        <v>554</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -18994,7 +18994,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>854</v>
+        <v>994</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -19014,7 +19014,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>550</v>
+        <v>476</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -19034,7 +19034,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>785</v>
+        <v>557</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -19054,7 +19054,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>229</v>
+        <v>254</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -19074,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>528</v>
+        <v>660</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -19094,7 +19094,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>634</v>
+        <v>476</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -19114,7 +19114,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>633</v>
+        <v>587</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -19134,7 +19134,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>885</v>
+        <v>731</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -19154,7 +19154,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>627</v>
+        <v>683</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -19174,7 +19174,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>858</v>
+        <v>657</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -19194,7 +19194,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>275</v>
+        <v>668</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -19214,7 +19214,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -19234,7 +19234,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>449</v>
+        <v>610</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -19254,7 +19254,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>672</v>
+        <v>614</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -19274,7 +19274,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>937</v>
+        <v>588</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -19294,7 +19294,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>286</v>
+        <v>992</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -19314,7 +19314,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>269</v>
+        <v>558</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -19334,7 +19334,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>969</v>
+        <v>738</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -19354,7 +19354,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>566</v>
+        <v>657</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -19374,7 +19374,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>913</v>
+        <v>730</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -19394,7 +19394,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>232</v>
+        <v>675</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -19414,7 +19414,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>459</v>
+        <v>644</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -19434,7 +19434,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>535</v>
+        <v>434</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -19454,7 +19454,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>850</v>
+        <v>401</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -19474,7 +19474,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>930</v>
+        <v>715</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -19494,7 +19494,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>482</v>
+        <v>664</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -19514,7 +19514,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>582</v>
+        <v>491</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -19534,7 +19534,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>282</v>
+        <v>992</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -19554,7 +19554,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>662</v>
+        <v>609</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -19574,7 +19574,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>913</v>
+        <v>571</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -19594,7 +19594,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>849</v>
+        <v>615</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -19614,7 +19614,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>943</v>
+        <v>974</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -19634,7 +19634,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>903</v>
+        <v>641</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -19654,7 +19654,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>793</v>
+        <v>883</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -19674,7 +19674,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>485</v>
+        <v>594</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -19694,7 +19694,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>593</v>
+        <v>340</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -19714,7 +19714,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>353</v>
+        <v>619</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -19734,7 +19734,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>716</v>
+        <v>702</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -19754,7 +19754,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>300</v>
+        <v>914</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -19774,7 +19774,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>684</v>
+        <v>596</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -19794,7 +19794,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>492</v>
+        <v>675</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -19814,7 +19814,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>811</v>
+        <v>727</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -19834,7 +19834,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>959</v>
+        <v>253</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -19854,7 +19854,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>318</v>
+        <v>656</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -19874,7 +19874,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>821</v>
+        <v>572</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -19894,7 +19894,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>769</v>
+        <v>902</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -19914,7 +19914,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>376</v>
+        <v>447</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -19934,7 +19934,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>434</v>
+        <v>484</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -19954,7 +19954,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>389</v>
+        <v>971</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -19974,7 +19974,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>739</v>
+        <v>912</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -19994,7 +19994,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>287</v>
+        <v>312</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -20014,7 +20014,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>521</v>
+        <v>414</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -20034,7 +20034,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>426</v>
+        <v>894</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -20054,7 +20054,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>976</v>
+        <v>776</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -20074,7 +20074,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>675</v>
+        <v>839</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -20094,7 +20094,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>715</v>
+        <v>655</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -20114,7 +20114,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>565</v>
+        <v>646</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -20134,7 +20134,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>389</v>
+        <v>284</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -20154,7 +20154,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>613</v>
+        <v>399</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -20174,7 +20174,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>619</v>
+        <v>323</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -20194,7 +20194,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>575</v>
+        <v>284</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -20214,7 +20214,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>466</v>
+        <v>944</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -20234,7 +20234,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>952</v>
+        <v>798</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -20254,7 +20254,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>857</v>
+        <v>691</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -20274,7 +20274,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>320</v>
+        <v>857</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -20294,7 +20294,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>274</v>
+        <v>429</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -20314,7 +20314,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>221</v>
+        <v>387</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -20334,7 +20334,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>840</v>
+        <v>466</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -20354,7 +20354,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>655</v>
+        <v>824</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -20374,7 +20374,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>884</v>
+        <v>303</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -20394,7 +20394,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>481</v>
+        <v>320</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -20414,7 +20414,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>435</v>
+        <v>613</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -20434,7 +20434,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>959</v>
+        <v>954</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -20454,7 +20454,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>294</v>
+        <v>830</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -20474,7 +20474,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>761</v>
+        <v>449</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -20494,7 +20494,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>416</v>
+        <v>929</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -20514,7 +20514,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>907</v>
+        <v>393</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -20534,7 +20534,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>521</v>
+        <v>810</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -20554,7 +20554,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>273</v>
+        <v>721</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -20574,7 +20574,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>698</v>
+        <v>231</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -20594,7 +20594,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>250</v>
+        <v>354</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -20614,7 +20614,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>253</v>
+        <v>293</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -20634,7 +20634,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>500</v>
+        <v>479</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -20654,7 +20654,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>425</v>
+        <v>935</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -20674,7 +20674,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>781</v>
+        <v>415</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -20694,7 +20694,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>381</v>
+        <v>892</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -20714,7 +20714,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>700</v>
+        <v>961</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -20734,7 +20734,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>435</v>
+        <v>819</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -20754,7 +20754,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>700</v>
+        <v>981</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -20774,7 +20774,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>611</v>
+        <v>444</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -20794,7 +20794,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>967</v>
+        <v>227</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -20814,7 +20814,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>779</v>
+        <v>570</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -20834,7 +20834,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>492</v>
+        <v>734</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -20854,7 +20854,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>414</v>
+        <v>299</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -20874,7 +20874,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>554</v>
+        <v>303</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -20894,7 +20894,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>201</v>
+        <v>862</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -20914,7 +20914,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>308</v>
+        <v>903</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -20934,7 +20934,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>890</v>
+        <v>901</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -20954,7 +20954,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>619</v>
+        <v>307</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -20974,7 +20974,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>365</v>
+        <v>723</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -20994,7 +20994,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>402</v>
+        <v>308</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -21014,7 +21014,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>300</v>
+        <v>524</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -21034,7 +21034,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>224</v>
+        <v>797</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -21054,7 +21054,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>884</v>
+        <v>689</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -21074,7 +21074,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>289</v>
+        <v>555</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -21094,7 +21094,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>877</v>
+        <v>577</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -21114,7 +21114,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>209</v>
+        <v>738</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -21134,7 +21134,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>312</v>
+        <v>498</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -21154,7 +21154,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>966</v>
+        <v>505</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -21174,7 +21174,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>649</v>
+        <v>632</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -21194,7 +21194,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>881</v>
+        <v>661</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -21214,7 +21214,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>705</v>
+        <v>371</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -21234,7 +21234,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>864</v>
+        <v>568</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -21254,7 +21254,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>567</v>
+        <v>681</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -21274,7 +21274,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>521</v>
+        <v>878</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -21294,7 +21294,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>513</v>
+        <v>274</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -21314,7 +21314,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>905</v>
+        <v>247</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -21334,7 +21334,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>520</v>
+        <v>795</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -21354,7 +21354,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>232</v>
+        <v>207</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -21374,7 +21374,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>208</v>
+        <v>896</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -21394,7 +21394,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>702</v>
+        <v>270</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -21414,7 +21414,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>952</v>
+        <v>748</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -21434,7 +21434,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>741</v>
+        <v>369</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -21454,7 +21454,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>521</v>
+        <v>411</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -21474,7 +21474,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>923</v>
+        <v>856</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -21494,7 +21494,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>843</v>
+        <v>513</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -21514,7 +21514,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>534</v>
+        <v>341</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -21534,7 +21534,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>779</v>
+        <v>268</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -21554,7 +21554,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>978</v>
+        <v>690</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -21574,7 +21574,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>268</v>
+        <v>840</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -21594,7 +21594,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>377</v>
+        <v>318</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -21614,7 +21614,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>856</v>
+        <v>598</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -21634,7 +21634,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>348</v>
+        <v>541</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -21654,7 +21654,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>804</v>
+        <v>543</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -21674,7 +21674,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>930</v>
+        <v>260</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -21694,7 +21694,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>544</v>
+        <v>292</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -21714,7 +21714,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>392</v>
+        <v>693</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -21734,7 +21734,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -21754,7 +21754,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>248</v>
+        <v>649</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -21774,7 +21774,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>832</v>
+        <v>719</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -21794,7 +21794,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>487</v>
+        <v>975</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -21814,7 +21814,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>765</v>
+        <v>926</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -21834,7 +21834,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>623</v>
+        <v>698</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -21854,7 +21854,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>764</v>
+        <v>459</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -21874,7 +21874,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>488</v>
+        <v>849</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -21894,7 +21894,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>207</v>
+        <v>321</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -21914,7 +21914,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>858</v>
+        <v>532</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -21934,7 +21934,7 @@
         <v>10</v>
       </c>
       <c r="F397">
-        <v>655</v>
+        <v>476</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -21954,7 +21954,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>232</v>
+        <v>718</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -21974,7 +21974,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>625</v>
+        <v>873</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -21994,7 +21994,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>767</v>
+        <v>916</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -22014,7 +22014,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>395</v>
+        <v>715</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -22034,7 +22034,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>623</v>
+        <v>233</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -22054,7 +22054,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>504</v>
+        <v>965</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -22074,7 +22074,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>549</v>
+        <v>227</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -22094,7 +22094,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>669</v>
+        <v>539</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -22114,7 +22114,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>211</v>
+        <v>397</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -22134,7 +22134,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>311</v>
+        <v>270</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -22154,7 +22154,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>832</v>
+        <v>821</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -22174,7 +22174,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>377</v>
+        <v>935</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -22194,7 +22194,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>335</v>
+        <v>857</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -22214,7 +22214,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>697</v>
+        <v>335</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -22234,7 +22234,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>820</v>
+        <v>904</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -22254,7 +22254,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>527</v>
+        <v>595</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -22274,7 +22274,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>809</v>
+        <v>304</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -22294,7 +22294,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>713</v>
+        <v>468</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -22314,7 +22314,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>315</v>
+        <v>509</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -22334,7 +22334,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>940</v>
+        <v>603</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -22354,7 +22354,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>225</v>
+        <v>510</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -22374,7 +22374,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>578</v>
+        <v>426</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -22394,7 +22394,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>934</v>
+        <v>659</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -22414,7 +22414,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>235</v>
+        <v>554</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -22434,7 +22434,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>456</v>
+        <v>507</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -22454,7 +22454,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>906</v>
+        <v>558</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -22474,7 +22474,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>800</v>
+        <v>213</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -22494,7 +22494,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>789</v>
+        <v>816</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -22514,7 +22514,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>291</v>
+        <v>338</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -22534,7 +22534,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>222</v>
+        <v>834</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -22554,7 +22554,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>927</v>
+        <v>254</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -22574,7 +22574,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>923</v>
+        <v>680</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -22594,7 +22594,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>703</v>
+        <v>616</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -22614,7 +22614,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>856</v>
+        <v>816</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -22634,7 +22634,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>344</v>
+        <v>860</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -22654,7 +22654,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>927</v>
+        <v>307</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -22674,7 +22674,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>342</v>
+        <v>953</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -22694,7 +22694,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>698</v>
+        <v>792</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -22714,7 +22714,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>362</v>
+        <v>936</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -22734,7 +22734,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>668</v>
+        <v>789</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -22754,7 +22754,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>892</v>
+        <v>908</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -22774,7 +22774,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>493</v>
+        <v>685</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -22794,7 +22794,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>731</v>
+        <v>326</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -22814,7 +22814,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>360</v>
+        <v>211</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -22834,7 +22834,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>421</v>
+        <v>867</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>829</v>
+        <v>274</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -22874,7 +22874,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>268</v>
+        <v>408</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -22894,7 +22894,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>928</v>
+        <v>344</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -22914,7 +22914,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>853</v>
+        <v>969</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -22934,7 +22934,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>938</v>
+        <v>722</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -22954,7 +22954,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>576</v>
+        <v>599</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -22974,7 +22974,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>575</v>
+        <v>588</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>525</v>
+        <v>418</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -23014,7 +23014,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>812</v>
+        <v>708</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -23034,7 +23034,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>503</v>
+        <v>314</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -23054,7 +23054,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>854</v>
+        <v>438</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -23074,7 +23074,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>999</v>
+        <v>441</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -23094,7 +23094,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>321</v>
+        <v>333</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -23114,7 +23114,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>820</v>
+        <v>317</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>802</v>
+        <v>947</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -23154,7 +23154,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>725</v>
+        <v>876</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -23174,7 +23174,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -23194,7 +23194,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>242</v>
+        <v>529</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -23214,7 +23214,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>676</v>
+        <v>480</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -23234,7 +23234,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>978</v>
+        <v>408</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -23254,7 +23254,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>571</v>
+        <v>885</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>246</v>
+        <v>382</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -23294,7 +23294,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>942</v>
+        <v>266</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -23314,7 +23314,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>598</v>
+        <v>527</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -23334,7 +23334,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -23354,7 +23354,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>266</v>
+        <v>648</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -23374,7 +23374,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>296</v>
+        <v>637</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -23394,7 +23394,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>501</v>
+        <v>327</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>931</v>
+        <v>777</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -23434,7 +23434,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>613</v>
+        <v>348</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -23454,7 +23454,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>367</v>
+        <v>852</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -23474,7 +23474,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -23494,7 +23494,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>250</v>
+        <v>572</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -23514,7 +23514,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>803</v>
+        <v>936</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -23534,7 +23534,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>413</v>
+        <v>648</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>890</v>
+        <v>996</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -23574,7 +23574,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>721</v>
+        <v>418</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -23594,7 +23594,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>354</v>
+        <v>877</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -23614,7 +23614,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>516</v>
+        <v>283</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -23634,7 +23634,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>587</v>
+        <v>559</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -23654,7 +23654,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>799</v>
+        <v>882</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -23674,7 +23674,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>805</v>
+        <v>579</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>990</v>
+        <v>879</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -23714,7 +23714,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>952</v>
+        <v>899</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -23734,7 +23734,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>445</v>
+        <v>926</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -23754,7 +23754,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>713</v>
+        <v>724</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -23774,7 +23774,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>722</v>
+        <v>898</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -23794,7 +23794,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>695</v>
+        <v>653</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -23814,7 +23814,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>229</v>
+        <v>292</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>327</v>
+        <v>440</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -23854,7 +23854,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>975</v>
+        <v>754</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -23874,7 +23874,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>304</v>
+        <v>998</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -23894,7 +23894,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>662</v>
+        <v>743</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -23914,7 +23914,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>498</v>
+        <v>431</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -23934,7 +23934,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>529</v>
+        <v>818</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -23954,7 +23954,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>652</v>
+        <v>580</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>657</v>
+        <v>364</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -23994,7 +23994,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>453</v>
+        <v>287</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -24014,7 +24014,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>299</v>
+        <v>418</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -24034,7 +24034,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>859</v>
+        <v>238</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -24054,7 +24054,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>849</v>
+        <v>405</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -24074,7 +24074,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>969</v>
+        <v>760</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -24094,7 +24094,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>268</v>
+        <v>405</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>244</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -24264,7 +24264,7 @@
         <v>622</v>
       </c>
       <c r="F2">
-        <v>562</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -24284,7 +24284,7 @@
         <v>622</v>
       </c>
       <c r="F3">
-        <v>718</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/Excel/Automation_Test_Report.xlsx
@@ -3208,13 +3208,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>BUILD-88</t>
+    <t>BUILD-89</t>
   </si>
   <si>
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>9/13/2026, 2:40:32 AM</t>
+    <t>9/14/2026, 2:58:14 AM</t>
   </si>
   <si>
     <t>Target Device</t>
@@ -3793,7 +3793,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>555</v>
+        <v>611</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3813,7 +3813,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>351</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>739</v>
+        <v>746</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3853,7 +3853,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>592</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3873,7 +3873,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>227</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3893,7 +3893,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>855</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3913,7 +3913,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>937</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3933,7 +3933,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>354</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3953,7 +3953,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>585</v>
+        <v>926</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3973,7 +3973,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>842</v>
+        <v>728</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3993,7 +3993,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>747</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4013,7 +4013,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>539</v>
+        <v>851</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4033,7 +4033,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4053,7 +4053,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>229</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4073,7 +4073,7 @@
         <v>41</v>
       </c>
       <c r="F16">
-        <v>741</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4093,7 +4093,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>611</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4113,7 +4113,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>646</v>
+        <v>928</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4133,7 +4133,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>994</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4153,7 +4153,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>867</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4173,7 +4173,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4193,7 +4193,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>963</v>
+        <v>836</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4213,7 +4213,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>591</v>
+        <v>709</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4233,7 +4233,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>773</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4253,7 +4253,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>958</v>
+        <v>244</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4273,7 +4273,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>466</v>
+        <v>882</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4293,7 +4293,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>725</v>
+        <v>605</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>810</v>
+        <v>662</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>829</v>
+        <v>569</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4353,7 +4353,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>315</v>
+        <v>735</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4373,7 +4373,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>437</v>
+        <v>391</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4393,7 +4393,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>906</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4413,7 +4413,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>401</v>
+        <v>937</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4433,7 +4433,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>369</v>
+        <v>761</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>379</v>
+        <v>959</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4473,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>918</v>
+        <v>563</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4493,7 +4493,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>473</v>
+        <v>440</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4513,7 +4513,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>660</v>
+        <v>875</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4533,7 +4533,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>891</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4553,7 +4553,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>216</v>
+        <v>717</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4573,7 +4573,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>553</v>
+        <v>637</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4593,7 +4593,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>247</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4613,7 +4613,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>488</v>
+        <v>512</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,7 +4633,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>904</v>
+        <v>825</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4653,7 +4653,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>614</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4673,7 +4673,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>218</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4693,7 +4693,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>568</v>
+        <v>515</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4713,7 +4713,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>985</v>
+        <v>461</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4733,7 +4733,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>930</v>
+        <v>806</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4753,7 +4753,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>881</v>
+        <v>850</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>532</v>
+        <v>954</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4793,7 +4793,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>517</v>
+        <v>896</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4813,7 +4813,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>204</v>
+        <v>389</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4833,7 +4833,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>747</v>
+        <v>332</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>309</v>
+        <v>924</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4873,7 +4873,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>929</v>
+        <v>712</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>528</v>
+        <v>432</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4913,7 +4913,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>241</v>
+        <v>584</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4933,7 +4933,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>293</v>
+        <v>931</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4953,7 +4953,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>423</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4973,7 +4973,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>490</v>
+        <v>578</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4993,7 +4993,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>553</v>
+        <v>575</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -5013,7 +5013,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>969</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -5033,7 +5033,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -5053,7 +5053,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>793</v>
+        <v>691</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -5073,7 +5073,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>804</v>
+        <v>480</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -5093,7 +5093,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>952</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -5113,7 +5113,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>810</v>
+        <v>788</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5133,7 +5133,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>351</v>
+        <v>986</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -5153,7 +5153,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>681</v>
+        <v>713</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -5173,7 +5173,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>661</v>
+        <v>263</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -5193,7 +5193,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>422</v>
+        <v>610</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -5213,7 +5213,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>930</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -5233,7 +5233,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>507</v>
+        <v>716</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -5253,7 +5253,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>596</v>
+        <v>695</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -5273,7 +5273,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>359</v>
+        <v>291</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5293,7 +5293,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>929</v>
+        <v>956</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5313,7 +5313,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>239</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5333,7 +5333,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>505</v>
+        <v>679</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5353,7 +5353,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>259</v>
+        <v>721</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5373,7 +5373,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>279</v>
+        <v>831</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5393,7 +5393,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>428</v>
+        <v>528</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5413,7 +5413,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>845</v>
+        <v>885</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5433,7 +5433,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>987</v>
+        <v>484</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5453,7 +5453,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>487</v>
+        <v>391</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5473,7 +5473,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>715</v>
+        <v>392</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5493,7 +5493,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>436</v>
+        <v>403</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5513,7 +5513,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>580</v>
+        <v>991</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5533,7 +5533,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>882</v>
+        <v>537</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5553,7 +5553,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>466</v>
+        <v>657</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -5573,7 +5573,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>985</v>
+        <v>864</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -5593,7 +5593,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>516</v>
+        <v>346</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5613,7 +5613,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>912</v>
+        <v>735</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5633,7 +5633,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>248</v>
+        <v>801</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>965</v>
+        <v>488</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>820</v>
+        <v>429</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5693,7 +5693,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>646</v>
+        <v>984</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -5713,7 +5713,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>591</v>
+        <v>892</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -5733,7 +5733,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -5753,7 +5753,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>228</v>
+        <v>970</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5773,7 +5773,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>997</v>
+        <v>209</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -5793,7 +5793,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>351</v>
+        <v>762</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -5813,7 +5813,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>551</v>
+        <v>284</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5833,7 +5833,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -5853,7 +5853,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>763</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -5873,7 +5873,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>201</v>
+        <v>813</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -5893,7 +5893,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>743</v>
+        <v>822</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -5913,7 +5913,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>822</v>
+        <v>472</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -5933,7 +5933,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>618</v>
+        <v>475</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -5953,7 +5953,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>809</v>
+        <v>529</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5973,7 +5973,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>418</v>
+        <v>733</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -5993,7 +5993,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>672</v>
+        <v>708</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -6013,7 +6013,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>724</v>
+        <v>276</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -6033,7 +6033,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>990</v>
+        <v>670</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -6053,7 +6053,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>755</v>
+        <v>843</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -6073,7 +6073,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>442</v>
+        <v>738</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -6093,7 +6093,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>421</v>
+        <v>468</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -6113,7 +6113,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>480</v>
+        <v>631</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -6133,7 +6133,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>893</v>
+        <v>496</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -6153,7 +6153,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>512</v>
+        <v>780</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -6173,7 +6173,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>923</v>
+        <v>745</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -6193,7 +6193,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>587</v>
+        <v>968</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -6213,7 +6213,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>743</v>
+        <v>899</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -6233,7 +6233,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>860</v>
+        <v>386</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -6253,7 +6253,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>278</v>
+        <v>718</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -6273,7 +6273,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>904</v>
+        <v>340</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6293,7 +6293,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>794</v>
+        <v>968</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6313,7 +6313,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>928</v>
+        <v>265</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6333,7 +6333,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>408</v>
+        <v>543</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6353,7 +6353,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>412</v>
+        <v>729</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6373,7 +6373,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>860</v>
+        <v>453</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6393,7 +6393,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>304</v>
+        <v>792</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6413,7 +6413,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>876</v>
+        <v>533</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -6433,7 +6433,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>273</v>
+        <v>872</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -6453,7 +6453,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>682</v>
+        <v>295</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6473,7 +6473,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>698</v>
+        <v>838</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6493,7 +6493,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>745</v>
+        <v>947</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6513,7 +6513,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>365</v>
+        <v>712</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -6533,7 +6533,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>404</v>
+        <v>902</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>927</v>
+        <v>702</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6573,7 +6573,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>666</v>
+        <v>632</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6593,7 +6593,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>324</v>
+        <v>850</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -6613,7 +6613,7 @@
         <v>41</v>
       </c>
       <c r="F143">
-        <v>980</v>
+        <v>740</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -6633,7 +6633,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>818</v>
+        <v>768</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -6653,7 +6653,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>803</v>
+        <v>345</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>968</v>
+        <v>530</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -6693,7 +6693,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>833</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -6713,7 +6713,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>415</v>
+        <v>677</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -6733,7 +6733,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>500</v>
+        <v>224</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6753,7 +6753,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>607</v>
+        <v>633</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -6773,7 +6773,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>257</v>
+        <v>977</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -6793,7 +6793,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>773</v>
+        <v>741</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6813,7 +6813,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>730</v>
+        <v>860</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -6833,7 +6833,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>530</v>
+        <v>330</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -6853,7 +6853,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>767</v>
+        <v>977</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -6873,7 +6873,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>531</v>
+        <v>808</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>443</v>
+        <v>930</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6913,7 +6913,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>548</v>
+        <v>432</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -6933,7 +6933,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>744</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -6953,7 +6953,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>463</v>
+        <v>965</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -6973,7 +6973,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>346</v>
+        <v>930</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -6993,7 +6993,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>678</v>
+        <v>805</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -7013,7 +7013,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>769</v>
+        <v>652</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -7033,7 +7033,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>928</v>
+        <v>962</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -7053,7 +7053,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>329</v>
+        <v>222</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -7073,7 +7073,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>883</v>
+        <v>462</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -7093,7 +7093,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>487</v>
+        <v>244</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -7113,7 +7113,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>609</v>
+        <v>348</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -7133,7 +7133,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>745</v>
+        <v>845</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -7153,7 +7153,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>666</v>
+        <v>725</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -7173,7 +7173,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>408</v>
+        <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -7193,7 +7193,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>890</v>
+        <v>625</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -7213,7 +7213,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>798</v>
+        <v>427</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>815</v>
+        <v>956</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -7253,7 +7253,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>868</v>
+        <v>760</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -7273,7 +7273,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>645</v>
+        <v>350</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7293,7 +7293,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>840</v>
+        <v>513</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7313,7 +7313,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7333,7 +7333,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>739</v>
+        <v>470</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7353,7 +7353,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>253</v>
+        <v>477</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7373,7 +7373,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>315</v>
+        <v>517</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7393,7 +7393,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>520</v>
+        <v>598</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7413,7 +7413,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>773</v>
+        <v>934</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7433,7 +7433,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>453</v>
+        <v>673</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -7453,7 +7453,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>823</v>
+        <v>831</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -7473,7 +7473,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>390</v>
+        <v>785</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>467</v>
+        <v>766</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -7513,7 +7513,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>214</v>
+        <v>479</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7533,7 +7533,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>704</v>
+        <v>979</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -7553,7 +7553,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>439</v>
+        <v>421</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>708</v>
+        <v>472</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -7593,7 +7593,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>293</v>
+        <v>351</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -7613,7 +7613,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>320</v>
+        <v>482</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -7633,7 +7633,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>809</v>
+        <v>607</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -7653,7 +7653,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>526</v>
+        <v>630</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -7673,7 +7673,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>587</v>
+        <v>639</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -7693,7 +7693,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>760</v>
+        <v>535</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -7713,7 +7713,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>400</v>
+        <v>704</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -7733,7 +7733,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>265</v>
+        <v>648</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -7753,7 +7753,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>263</v>
+        <v>923</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -7773,7 +7773,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>213</v>
+        <v>771</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -7793,7 +7793,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>398</v>
+        <v>651</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -7813,7 +7813,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>331</v>
+        <v>833</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -7833,7 +7833,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>574</v>
+        <v>916</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7853,7 +7853,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>323</v>
+        <v>713</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7873,7 +7873,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>995</v>
+        <v>463</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -7893,7 +7893,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>296</v>
+        <v>650</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -7913,7 +7913,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>748</v>
+        <v>376</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -7933,7 +7933,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>929</v>
+        <v>753</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -7953,7 +7953,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>280</v>
+        <v>801</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -7973,7 +7973,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>805</v>
+        <v>674</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7993,7 +7993,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>761</v>
+        <v>864</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -8013,7 +8013,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>919</v>
+        <v>900</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -8033,7 +8033,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>943</v>
+        <v>447</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -8053,7 +8053,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>892</v>
+        <v>595</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -8073,7 +8073,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>246</v>
+        <v>654</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -8093,7 +8093,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>400</v>
+        <v>334</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -8113,7 +8113,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>839</v>
+        <v>913</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -8133,7 +8133,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>298</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -8153,7 +8153,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>318</v>
+        <v>805</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -8173,7 +8173,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>361</v>
+        <v>341</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -8193,7 +8193,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>212</v>
+        <v>354</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -8213,7 +8213,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>772</v>
+        <v>780</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -8233,7 +8233,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>774</v>
+        <v>802</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -8253,7 +8253,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>503</v>
+        <v>201</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8273,7 +8273,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>902</v>
+        <v>658</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8293,7 +8293,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>366</v>
+        <v>264</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8313,7 +8313,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>213</v>
+        <v>834</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8333,7 +8333,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>992</v>
+        <v>881</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -8353,7 +8353,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>784</v>
+        <v>475</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8373,7 +8373,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>907</v>
+        <v>467</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8393,7 +8393,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>240</v>
+        <v>630</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>449</v>
+        <v>696</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8433,7 +8433,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>795</v>
+        <v>296</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -8453,7 +8453,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>303</v>
+        <v>677</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -8473,7 +8473,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>791</v>
+        <v>933</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -8493,7 +8493,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>779</v>
+        <v>827</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -8513,7 +8513,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>971</v>
+        <v>753</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -8533,7 +8533,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>935</v>
+        <v>531</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -8553,7 +8553,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>637</v>
+        <v>311</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8573,7 +8573,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>215</v>
+        <v>264</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -8593,7 +8593,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -8613,7 +8613,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>429</v>
+        <v>915</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -8633,7 +8633,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>513</v>
+        <v>228</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8653,7 +8653,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>827</v>
+        <v>299</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8673,7 +8673,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>498</v>
+        <v>593</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -8693,7 +8693,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -8713,7 +8713,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>728</v>
+        <v>462</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8733,7 +8733,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>496</v>
+        <v>590</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -8753,7 +8753,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>596</v>
+        <v>381</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8773,7 +8773,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>554</v>
+        <v>946</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8793,7 +8793,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>994</v>
+        <v>712</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8813,7 +8813,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>476</v>
+        <v>713</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -8833,7 +8833,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>557</v>
+        <v>450</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -8853,7 +8853,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>254</v>
+        <v>981</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>660</v>
+        <v>856</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -8893,7 +8893,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>476</v>
+        <v>837</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -8913,7 +8913,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>587</v>
+        <v>694</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -8933,7 +8933,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>731</v>
+        <v>690</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -8953,7 +8953,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>683</v>
+        <v>540</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -8973,7 +8973,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>657</v>
+        <v>740</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -8993,7 +8993,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>668</v>
+        <v>938</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -9013,7 +9013,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>537</v>
+        <v>615</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -9033,7 +9033,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>610</v>
+        <v>514</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -9053,7 +9053,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>614</v>
+        <v>726</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -9073,7 +9073,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>588</v>
+        <v>474</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -9093,7 +9093,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>992</v>
+        <v>802</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -9113,7 +9113,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>558</v>
+        <v>825</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -9133,7 +9133,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>738</v>
+        <v>770</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -9153,7 +9153,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>657</v>
+        <v>314</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -9173,7 +9173,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>730</v>
+        <v>676</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -9193,7 +9193,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>675</v>
+        <v>933</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -9213,7 +9213,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>644</v>
+        <v>748</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -9233,7 +9233,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>434</v>
+        <v>324</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -9253,7 +9253,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>401</v>
+        <v>448</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -9273,7 +9273,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>715</v>
+        <v>366</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -9293,7 +9293,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>664</v>
+        <v>283</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -9313,7 +9313,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>491</v>
+        <v>639</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -9333,7 +9333,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>992</v>
+        <v>957</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -9353,7 +9353,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>609</v>
+        <v>279</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -9373,7 +9373,7 @@
         <v>41</v>
       </c>
       <c r="F281">
-        <v>430</v>
+        <v>520</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -9393,7 +9393,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>571</v>
+        <v>465</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -9413,7 +9413,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>615</v>
+        <v>337</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -9433,7 +9433,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>974</v>
+        <v>506</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -9453,7 +9453,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>641</v>
+        <v>684</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -9473,7 +9473,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>883</v>
+        <v>453</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -9493,7 +9493,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>594</v>
+        <v>382</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -9513,7 +9513,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>340</v>
+        <v>989</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -9533,7 +9533,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>619</v>
+        <v>630</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -9553,7 +9553,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>702</v>
+        <v>314</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -9573,7 +9573,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>914</v>
+        <v>728</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -9593,7 +9593,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>596</v>
+        <v>562</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -9613,7 +9613,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>675</v>
+        <v>406</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -9633,7 +9633,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>727</v>
+        <v>886</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -9653,7 +9653,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>253</v>
+        <v>646</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -9673,7 +9673,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>656</v>
+        <v>502</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -9693,7 +9693,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>572</v>
+        <v>225</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -9713,7 +9713,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>902</v>
+        <v>368</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -9733,7 +9733,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>447</v>
+        <v>710</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -9753,7 +9753,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>484</v>
+        <v>727</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -9773,7 +9773,7 @@
         <v>622</v>
       </c>
       <c r="F301">
-        <v>527</v>
+        <v>333</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -9793,7 +9793,7 @@
         <v>622</v>
       </c>
       <c r="F302">
-        <v>459</v>
+        <v>557</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -9813,7 +9813,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>971</v>
+        <v>859</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -9833,7 +9833,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>912</v>
+        <v>546</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -9853,7 +9853,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>312</v>
+        <v>209</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -9873,7 +9873,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>414</v>
+        <v>503</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -9893,7 +9893,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>894</v>
+        <v>727</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -9913,7 +9913,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>776</v>
+        <v>918</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -9933,7 +9933,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>839</v>
+        <v>434</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>655</v>
+        <v>448</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -9973,7 +9973,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>646</v>
+        <v>955</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -9993,7 +9993,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>284</v>
+        <v>849</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -10013,7 +10013,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>399</v>
+        <v>741</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -10033,7 +10033,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>323</v>
+        <v>775</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -10053,7 +10053,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>284</v>
+        <v>235</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -10073,7 +10073,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>944</v>
+        <v>244</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -10093,7 +10093,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>798</v>
+        <v>668</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -10113,7 +10113,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>691</v>
+        <v>375</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -10133,7 +10133,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>857</v>
+        <v>651</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>429</v>
+        <v>640</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -10173,7 +10173,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>387</v>
+        <v>832</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -10193,7 +10193,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>466</v>
+        <v>705</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -10213,7 +10213,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>824</v>
+        <v>487</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -10233,7 +10233,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -10253,7 +10253,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>320</v>
+        <v>219</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -10273,7 +10273,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>613</v>
+        <v>428</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -10293,7 +10293,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>954</v>
+        <v>374</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -10313,7 +10313,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>830</v>
+        <v>253</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -10333,7 +10333,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>449</v>
+        <v>220</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -10353,7 +10353,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>929</v>
+        <v>451</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -10373,7 +10373,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>393</v>
+        <v>574</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -10393,7 +10393,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>810</v>
+        <v>783</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -10413,7 +10413,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>721</v>
+        <v>343</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -10433,7 +10433,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>231</v>
+        <v>891</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -10453,7 +10453,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>354</v>
+        <v>548</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -10473,7 +10473,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>293</v>
+        <v>688</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -10493,7 +10493,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>479</v>
+        <v>676</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -10513,7 +10513,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>935</v>
+        <v>220</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -10533,7 +10533,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>415</v>
+        <v>245</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -10553,7 +10553,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>892</v>
+        <v>867</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -10573,7 +10573,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>961</v>
+        <v>935</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -10593,7 +10593,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>819</v>
+        <v>595</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -10613,7 +10613,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>981</v>
+        <v>923</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -10633,7 +10633,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>444</v>
+        <v>956</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -10653,7 +10653,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>227</v>
+        <v>316</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -10673,7 +10673,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>570</v>
+        <v>529</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -10693,7 +10693,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>734</v>
+        <v>631</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -10713,7 +10713,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>299</v>
+        <v>946</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -10733,7 +10733,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>303</v>
+        <v>750</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -10753,7 +10753,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>862</v>
+        <v>692</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -10773,7 +10773,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>903</v>
+        <v>802</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -10793,7 +10793,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>901</v>
+        <v>454</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -10813,7 +10813,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>307</v>
+        <v>679</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -10833,7 +10833,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>723</v>
+        <v>233</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -10853,7 +10853,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>308</v>
+        <v>814</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -10873,7 +10873,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>524</v>
+        <v>799</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -10893,7 +10893,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>797</v>
+        <v>511</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -10913,7 +10913,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>689</v>
+        <v>977</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -10933,7 +10933,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>555</v>
+        <v>521</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -10953,7 +10953,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>577</v>
+        <v>827</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -10973,7 +10973,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>738</v>
+        <v>310</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -10993,7 +10993,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>498</v>
+        <v>452</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -11013,7 +11013,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>505</v>
+        <v>667</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -11033,7 +11033,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>632</v>
+        <v>500</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -11053,7 +11053,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>661</v>
+        <v>213</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -11073,7 +11073,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>371</v>
+        <v>735</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -11093,7 +11093,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>568</v>
+        <v>816</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -11113,7 +11113,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>681</v>
+        <v>453</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -11133,7 +11133,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>878</v>
+        <v>907</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -11153,7 +11153,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>274</v>
+        <v>844</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -11173,7 +11173,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>247</v>
+        <v>779</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -11193,7 +11193,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>795</v>
+        <v>317</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -11213,7 +11213,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>207</v>
+        <v>731</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -11233,7 +11233,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>896</v>
+        <v>613</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -11253,7 +11253,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>270</v>
+        <v>743</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -11273,7 +11273,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>748</v>
+        <v>456</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -11293,7 +11293,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>369</v>
+        <v>915</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>411</v>
+        <v>741</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -11333,7 +11333,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>856</v>
+        <v>226</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -11353,7 +11353,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>513</v>
+        <v>689</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -11373,7 +11373,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>341</v>
+        <v>894</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -11393,7 +11393,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -11413,7 +11413,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>690</v>
+        <v>834</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -11433,7 +11433,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>840</v>
+        <v>397</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -11453,7 +11453,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>318</v>
+        <v>347</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -11473,7 +11473,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>598</v>
+        <v>506</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -11493,7 +11493,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>541</v>
+        <v>498</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -11513,7 +11513,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>543</v>
+        <v>375</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -11533,7 +11533,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>260</v>
+        <v>224</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -11553,7 +11553,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>292</v>
+        <v>786</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -11573,7 +11573,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>693</v>
+        <v>295</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -11593,7 +11593,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>240</v>
+        <v>952</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -11613,7 +11613,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>649</v>
+        <v>443</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -11633,7 +11633,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>719</v>
+        <v>455</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -11653,7 +11653,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>975</v>
+        <v>305</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -11673,7 +11673,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>926</v>
+        <v>476</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -11693,7 +11693,7 @@
         <v>10</v>
       </c>
       <c r="F397">
-        <v>698</v>
+        <v>609</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -11713,7 +11713,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>459</v>
+        <v>873</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -11733,7 +11733,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>849</v>
+        <v>605</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -11753,7 +11753,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>321</v>
+        <v>845</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -11773,7 +11773,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>532</v>
+        <v>722</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -11793,7 +11793,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>476</v>
+        <v>574</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -11813,7 +11813,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -11833,7 +11833,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>873</v>
+        <v>962</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>916</v>
+        <v>971</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -11873,7 +11873,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>715</v>
+        <v>276</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -11893,7 +11893,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>233</v>
+        <v>932</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -11913,7 +11913,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>965</v>
+        <v>589</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -11933,7 +11933,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>227</v>
+        <v>201</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -11953,7 +11953,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>539</v>
+        <v>829</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -11973,7 +11973,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>397</v>
+        <v>425</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -11993,7 +11993,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>270</v>
+        <v>721</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -12013,7 +12013,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>821</v>
+        <v>490</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -12033,7 +12033,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>935</v>
+        <v>810</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -12053,7 +12053,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>857</v>
+        <v>706</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -12073,7 +12073,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>335</v>
+        <v>682</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -12093,7 +12093,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>904</v>
+        <v>731</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -12113,7 +12113,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>595</v>
+        <v>575</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -12133,7 +12133,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>304</v>
+        <v>519</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -12153,7 +12153,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>468</v>
+        <v>223</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -12173,7 +12173,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>509</v>
+        <v>890</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -12193,7 +12193,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>603</v>
+        <v>699</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -12213,7 +12213,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>510</v>
+        <v>853</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -12233,7 +12233,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -12253,7 +12253,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>659</v>
+        <v>600</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -12273,7 +12273,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>554</v>
+        <v>475</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -12293,7 +12293,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -12313,7 +12313,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>558</v>
+        <v>426</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>213</v>
+        <v>999</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -12353,7 +12353,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>816</v>
+        <v>977</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -12373,7 +12373,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -12393,7 +12393,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>834</v>
+        <v>552</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -12413,7 +12413,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>254</v>
+        <v>732</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -12433,7 +12433,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>680</v>
+        <v>862</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -12453,7 +12453,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>616</v>
+        <v>362</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -12473,7 +12473,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>816</v>
+        <v>527</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -12493,7 +12493,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>860</v>
+        <v>988</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -12513,7 +12513,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>307</v>
+        <v>530</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12533,7 +12533,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>953</v>
+        <v>395</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12553,7 +12553,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>792</v>
+        <v>440</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12573,7 +12573,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>936</v>
+        <v>469</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12593,7 +12593,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>789</v>
+        <v>368</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -12613,7 +12613,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>908</v>
+        <v>747</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12633,7 +12633,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>685</v>
+        <v>776</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -12653,7 +12653,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>326</v>
+        <v>476</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -12673,7 +12673,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>211</v>
+        <v>250</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -12693,7 +12693,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>867</v>
+        <v>327</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12713,7 +12713,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>274</v>
+        <v>589</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12733,7 +12733,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>408</v>
+        <v>718</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -12753,7 +12753,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>344</v>
+        <v>636</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -12773,7 +12773,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>969</v>
+        <v>477</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -12793,7 +12793,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>722</v>
+        <v>486</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -12813,7 +12813,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>599</v>
+        <v>739</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -12833,7 +12833,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>588</v>
+        <v>924</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -12853,7 +12853,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>418</v>
+        <v>346</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -12873,7 +12873,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>708</v>
+        <v>528</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -12893,7 +12893,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>314</v>
+        <v>206</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -12913,7 +12913,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>438</v>
+        <v>649</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -12933,7 +12933,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>441</v>
+        <v>245</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -12953,7 +12953,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>333</v>
+        <v>610</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -12973,7 +12973,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>317</v>
+        <v>229</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -12993,7 +12993,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>947</v>
+        <v>531</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -13013,7 +13013,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>876</v>
+        <v>316</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -13033,7 +13033,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>349</v>
+        <v>784</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -13053,7 +13053,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>529</v>
+        <v>956</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -13073,7 +13073,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>480</v>
+        <v>203</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -13093,7 +13093,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>408</v>
+        <v>347</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -13113,7 +13113,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>885</v>
+        <v>963</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -13133,7 +13133,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>382</v>
+        <v>579</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -13153,7 +13153,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>266</v>
+        <v>362</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -13173,7 +13173,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>527</v>
+        <v>652</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -13193,7 +13193,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>445</v>
+        <v>357</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -13213,7 +13213,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>648</v>
+        <v>895</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -13233,7 +13233,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>637</v>
+        <v>327</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -13253,7 +13253,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>327</v>
+        <v>750</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -13273,7 +13273,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>777</v>
+        <v>984</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -13293,7 +13293,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>348</v>
+        <v>994</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -13313,7 +13313,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>852</v>
+        <v>535</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -13333,7 +13333,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>664</v>
+        <v>379</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -13353,7 +13353,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>572</v>
+        <v>995</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -13373,7 +13373,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>936</v>
+        <v>926</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -13393,7 +13393,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>648</v>
+        <v>942</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -13413,7 +13413,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>996</v>
+        <v>291</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -13433,7 +13433,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>418</v>
+        <v>220</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -13453,7 +13453,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>877</v>
+        <v>851</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -13473,7 +13473,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>283</v>
+        <v>330</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -13493,7 +13493,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>559</v>
+        <v>962</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -13513,7 +13513,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>882</v>
+        <v>202</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -13533,7 +13533,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>579</v>
+        <v>208</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -13553,7 +13553,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>879</v>
+        <v>924</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -13573,7 +13573,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>899</v>
+        <v>544</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -13593,7 +13593,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>926</v>
+        <v>491</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -13613,7 +13613,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>724</v>
+        <v>473</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -13633,7 +13633,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>898</v>
+        <v>804</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -13653,7 +13653,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>653</v>
+        <v>873</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13673,7 +13673,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>292</v>
+        <v>379</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -13693,7 +13693,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>440</v>
+        <v>456</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13713,7 +13713,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>754</v>
+        <v>257</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -13733,7 +13733,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>998</v>
+        <v>584</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -13753,7 +13753,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>743</v>
+        <v>451</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -13773,7 +13773,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>431</v>
+        <v>399</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -13793,7 +13793,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>818</v>
+        <v>456</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -13813,7 +13813,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>580</v>
+        <v>305</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -13833,7 +13833,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>364</v>
+        <v>217</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -13853,7 +13853,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>287</v>
+        <v>311</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -13873,7 +13873,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>418</v>
+        <v>447</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -13893,7 +13893,7 @@
         <v>10</v>
       </c>
       <c r="F507">
-        <v>238</v>
+        <v>924</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -13913,7 +13913,7 @@
         <v>10</v>
       </c>
       <c r="F508">
-        <v>405</v>
+        <v>342</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -13933,7 +13933,7 @@
         <v>10</v>
       </c>
       <c r="F509">
-        <v>760</v>
+        <v>865</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -13953,7 +13953,7 @@
         <v>10</v>
       </c>
       <c r="F510">
-        <v>405</v>
+        <v>803</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -13973,7 +13973,7 @@
         <v>10</v>
       </c>
       <c r="F511">
-        <v>674</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -14034,7 +14034,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>555</v>
+        <v>611</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -14054,7 +14054,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>351</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -14074,7 +14074,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>739</v>
+        <v>746</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -14094,7 +14094,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>592</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -14114,7 +14114,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>227</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -14134,7 +14134,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>855</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -14154,7 +14154,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>937</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -14174,7 +14174,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>354</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -14194,7 +14194,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>585</v>
+        <v>926</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -14214,7 +14214,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>842</v>
+        <v>728</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -14234,7 +14234,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>747</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -14254,7 +14254,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>539</v>
+        <v>851</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -14274,7 +14274,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -14294,7 +14294,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>229</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -14314,7 +14314,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>611</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -14334,7 +14334,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>646</v>
+        <v>928</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -14354,7 +14354,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>994</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -14374,7 +14374,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>867</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -14394,7 +14394,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -14414,7 +14414,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>963</v>
+        <v>836</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -14434,7 +14434,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>591</v>
+        <v>709</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -14454,7 +14454,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>773</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -14474,7 +14474,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>958</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -14494,7 +14494,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>466</v>
+        <v>882</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -14514,7 +14514,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>725</v>
+        <v>605</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -14534,7 +14534,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>810</v>
+        <v>662</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -14554,7 +14554,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>829</v>
+        <v>569</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -14574,7 +14574,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>315</v>
+        <v>735</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -14594,7 +14594,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>437</v>
+        <v>391</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -14614,7 +14614,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>906</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -14634,7 +14634,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>401</v>
+        <v>937</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -14654,7 +14654,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>369</v>
+        <v>761</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -14674,7 +14674,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>379</v>
+        <v>959</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -14694,7 +14694,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>918</v>
+        <v>563</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -14714,7 +14714,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>473</v>
+        <v>440</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -14734,7 +14734,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>660</v>
+        <v>875</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -14754,7 +14754,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>891</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -14774,7 +14774,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>216</v>
+        <v>717</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -14794,7 +14794,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>553</v>
+        <v>637</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -14814,7 +14814,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>247</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -14834,7 +14834,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>488</v>
+        <v>512</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -14854,7 +14854,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>904</v>
+        <v>825</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -14874,7 +14874,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>614</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -14894,7 +14894,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>218</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -14914,7 +14914,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>568</v>
+        <v>515</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -14934,7 +14934,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>985</v>
+        <v>461</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -14954,7 +14954,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>930</v>
+        <v>806</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -14974,7 +14974,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>881</v>
+        <v>850</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -14994,7 +14994,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>532</v>
+        <v>954</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -15014,7 +15014,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>517</v>
+        <v>896</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -15034,7 +15034,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>204</v>
+        <v>389</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -15054,7 +15054,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>747</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -15074,7 +15074,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>309</v>
+        <v>924</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -15094,7 +15094,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>929</v>
+        <v>712</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -15114,7 +15114,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>528</v>
+        <v>432</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -15134,7 +15134,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>241</v>
+        <v>584</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -15154,7 +15154,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>293</v>
+        <v>931</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -15174,7 +15174,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>423</v>
+        <v>503</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -15194,7 +15194,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>490</v>
+        <v>578</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -15214,7 +15214,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>553</v>
+        <v>575</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -15234,7 +15234,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>969</v>
+        <v>490</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -15254,7 +15254,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -15274,7 +15274,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>793</v>
+        <v>691</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -15294,7 +15294,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>804</v>
+        <v>480</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -15314,7 +15314,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>952</v>
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -15334,7 +15334,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>810</v>
+        <v>788</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -15354,7 +15354,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>351</v>
+        <v>986</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -15374,7 +15374,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>681</v>
+        <v>713</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -15394,7 +15394,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>661</v>
+        <v>263</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -15414,7 +15414,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>422</v>
+        <v>610</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -15434,7 +15434,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>930</v>
+        <v>264</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -15454,7 +15454,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>507</v>
+        <v>716</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -15474,7 +15474,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>596</v>
+        <v>695</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -15494,7 +15494,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>359</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -15514,7 +15514,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>929</v>
+        <v>956</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -15534,7 +15534,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>239</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -15554,7 +15554,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>505</v>
+        <v>679</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -15574,7 +15574,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>259</v>
+        <v>721</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -15594,7 +15594,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>279</v>
+        <v>831</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -15614,7 +15614,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>428</v>
+        <v>528</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -15634,7 +15634,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>845</v>
+        <v>885</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -15654,7 +15654,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>987</v>
+        <v>484</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -15674,7 +15674,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>487</v>
+        <v>391</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -15694,7 +15694,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>715</v>
+        <v>392</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -15714,7 +15714,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>436</v>
+        <v>403</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -15734,7 +15734,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>580</v>
+        <v>991</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -15754,7 +15754,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>882</v>
+        <v>537</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -15774,7 +15774,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>466</v>
+        <v>657</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -15794,7 +15794,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>985</v>
+        <v>864</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -15814,7 +15814,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>516</v>
+        <v>346</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -15834,7 +15834,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>912</v>
+        <v>735</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -15854,7 +15854,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>248</v>
+        <v>801</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -15874,7 +15874,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>965</v>
+        <v>488</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -15894,7 +15894,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>820</v>
+        <v>429</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -15914,7 +15914,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>646</v>
+        <v>984</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -15934,7 +15934,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>591</v>
+        <v>892</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -15954,7 +15954,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -15974,7 +15974,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>228</v>
+        <v>970</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -15994,7 +15994,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>997</v>
+        <v>209</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -16014,7 +16014,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>351</v>
+        <v>762</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -16034,7 +16034,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>551</v>
+        <v>284</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -16054,7 +16054,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -16074,7 +16074,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>763</v>
+        <v>300</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -16094,7 +16094,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>201</v>
+        <v>813</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -16114,7 +16114,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>743</v>
+        <v>822</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -16134,7 +16134,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>822</v>
+        <v>472</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -16154,7 +16154,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>618</v>
+        <v>475</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -16174,7 +16174,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>809</v>
+        <v>529</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -16194,7 +16194,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>418</v>
+        <v>733</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -16214,7 +16214,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>672</v>
+        <v>708</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -16234,7 +16234,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>724</v>
+        <v>276</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -16254,7 +16254,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>990</v>
+        <v>670</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -16274,7 +16274,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>755</v>
+        <v>843</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -16294,7 +16294,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>442</v>
+        <v>738</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -16314,7 +16314,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>421</v>
+        <v>468</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -16334,7 +16334,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>480</v>
+        <v>631</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -16354,7 +16354,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>893</v>
+        <v>496</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -16374,7 +16374,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>512</v>
+        <v>780</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -16394,7 +16394,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>923</v>
+        <v>745</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -16414,7 +16414,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>587</v>
+        <v>968</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -16434,7 +16434,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>743</v>
+        <v>899</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -16454,7 +16454,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>860</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -16474,7 +16474,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>278</v>
+        <v>718</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -16494,7 +16494,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>904</v>
+        <v>340</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -16514,7 +16514,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>794</v>
+        <v>968</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -16534,7 +16534,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>928</v>
+        <v>265</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -16554,7 +16554,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>408</v>
+        <v>543</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -16574,7 +16574,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>412</v>
+        <v>729</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -16594,7 +16594,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>860</v>
+        <v>453</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -16614,7 +16614,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>304</v>
+        <v>792</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -16634,7 +16634,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>876</v>
+        <v>533</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -16654,7 +16654,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>273</v>
+        <v>872</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -16674,7 +16674,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>682</v>
+        <v>295</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -16694,7 +16694,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>698</v>
+        <v>838</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -16714,7 +16714,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>745</v>
+        <v>947</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -16734,7 +16734,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>365</v>
+        <v>712</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -16754,7 +16754,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>404</v>
+        <v>902</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -16774,7 +16774,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>927</v>
+        <v>702</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -16794,7 +16794,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>666</v>
+        <v>632</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -16814,7 +16814,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>324</v>
+        <v>850</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -16834,7 +16834,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>818</v>
+        <v>768</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -16854,7 +16854,7 @@
         <v>10</v>
       </c>
       <c r="F143">
-        <v>803</v>
+        <v>345</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -16874,7 +16874,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>968</v>
+        <v>530</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -16894,7 +16894,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>833</v>
+        <v>224</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -16914,7 +16914,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>415</v>
+        <v>677</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -16934,7 +16934,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>500</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -16954,7 +16954,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>607</v>
+        <v>633</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -16974,7 +16974,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>257</v>
+        <v>977</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -16994,7 +16994,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>773</v>
+        <v>741</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -17014,7 +17014,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>730</v>
+        <v>860</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -17034,7 +17034,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>530</v>
+        <v>330</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -17054,7 +17054,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>767</v>
+        <v>977</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -17074,7 +17074,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>531</v>
+        <v>808</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -17094,7 +17094,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>443</v>
+        <v>930</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -17114,7 +17114,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>548</v>
+        <v>432</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -17134,7 +17134,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>744</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -17154,7 +17154,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>463</v>
+        <v>965</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -17174,7 +17174,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>346</v>
+        <v>930</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -17194,7 +17194,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>678</v>
+        <v>805</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -17214,7 +17214,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>769</v>
+        <v>652</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -17234,7 +17234,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>928</v>
+        <v>962</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -17254,7 +17254,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>329</v>
+        <v>222</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -17274,7 +17274,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>883</v>
+        <v>462</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -17294,7 +17294,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>487</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -17314,7 +17314,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>609</v>
+        <v>348</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -17334,7 +17334,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>745</v>
+        <v>845</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -17354,7 +17354,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>666</v>
+        <v>725</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -17374,7 +17374,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>408</v>
+        <v>305</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -17394,7 +17394,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>890</v>
+        <v>625</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -17414,7 +17414,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>798</v>
+        <v>427</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -17434,7 +17434,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>815</v>
+        <v>956</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -17454,7 +17454,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>868</v>
+        <v>760</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -17474,7 +17474,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>645</v>
+        <v>350</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -17494,7 +17494,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>840</v>
+        <v>513</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -17514,7 +17514,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -17534,7 +17534,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>739</v>
+        <v>470</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -17554,7 +17554,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>253</v>
+        <v>477</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -17574,7 +17574,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>315</v>
+        <v>517</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -17594,7 +17594,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>520</v>
+        <v>598</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -17614,7 +17614,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>773</v>
+        <v>934</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -17634,7 +17634,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>453</v>
+        <v>673</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -17654,7 +17654,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>823</v>
+        <v>831</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -17674,7 +17674,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>390</v>
+        <v>785</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -17694,7 +17694,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>467</v>
+        <v>766</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -17714,7 +17714,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>214</v>
+        <v>479</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -17734,7 +17734,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>704</v>
+        <v>979</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -17754,7 +17754,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>439</v>
+        <v>421</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -17774,7 +17774,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>708</v>
+        <v>472</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -17794,7 +17794,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>293</v>
+        <v>351</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -17814,7 +17814,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>320</v>
+        <v>482</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -17834,7 +17834,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>809</v>
+        <v>607</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -17854,7 +17854,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>526</v>
+        <v>630</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -17874,7 +17874,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>587</v>
+        <v>639</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -17894,7 +17894,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>760</v>
+        <v>535</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -17914,7 +17914,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>400</v>
+        <v>704</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -17934,7 +17934,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>265</v>
+        <v>648</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -17954,7 +17954,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>263</v>
+        <v>923</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -17974,7 +17974,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>213</v>
+        <v>771</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -17994,7 +17994,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>398</v>
+        <v>651</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -18014,7 +18014,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>331</v>
+        <v>833</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -18034,7 +18034,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>574</v>
+        <v>916</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -18054,7 +18054,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>323</v>
+        <v>713</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -18074,7 +18074,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>995</v>
+        <v>463</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -18094,7 +18094,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>296</v>
+        <v>650</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -18114,7 +18114,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>748</v>
+        <v>376</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -18134,7 +18134,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>929</v>
+        <v>753</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -18154,7 +18154,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>280</v>
+        <v>801</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -18174,7 +18174,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>805</v>
+        <v>674</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -18194,7 +18194,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>761</v>
+        <v>864</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -18214,7 +18214,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>919</v>
+        <v>900</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -18234,7 +18234,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>943</v>
+        <v>447</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -18254,7 +18254,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>892</v>
+        <v>595</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -18274,7 +18274,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>246</v>
+        <v>654</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -18294,7 +18294,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>400</v>
+        <v>334</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -18314,7 +18314,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>839</v>
+        <v>913</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -18334,7 +18334,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>298</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -18354,7 +18354,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>318</v>
+        <v>805</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -18374,7 +18374,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>361</v>
+        <v>341</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -18394,7 +18394,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>212</v>
+        <v>354</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -18414,7 +18414,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>772</v>
+        <v>780</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -18434,7 +18434,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>774</v>
+        <v>802</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -18454,7 +18454,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>503</v>
+        <v>201</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -18474,7 +18474,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>902</v>
+        <v>658</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -18494,7 +18494,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>366</v>
+        <v>264</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -18514,7 +18514,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>213</v>
+        <v>834</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -18534,7 +18534,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>992</v>
+        <v>881</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -18554,7 +18554,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>784</v>
+        <v>475</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -18574,7 +18574,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>907</v>
+        <v>467</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -18594,7 +18594,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>240</v>
+        <v>630</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -18614,7 +18614,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>449</v>
+        <v>696</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -18634,7 +18634,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>795</v>
+        <v>296</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -18654,7 +18654,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>303</v>
+        <v>677</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -18674,7 +18674,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>791</v>
+        <v>933</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -18694,7 +18694,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>779</v>
+        <v>827</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -18714,7 +18714,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>971</v>
+        <v>753</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -18734,7 +18734,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>935</v>
+        <v>531</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -18754,7 +18754,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>637</v>
+        <v>311</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -18774,7 +18774,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>215</v>
+        <v>264</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -18794,7 +18794,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -18814,7 +18814,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>429</v>
+        <v>915</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -18834,7 +18834,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>513</v>
+        <v>228</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -18854,7 +18854,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>827</v>
+        <v>299</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -18874,7 +18874,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>498</v>
+        <v>593</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -18894,7 +18894,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -18914,7 +18914,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>728</v>
+        <v>462</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -18934,7 +18934,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>496</v>
+        <v>590</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -18954,7 +18954,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>596</v>
+        <v>381</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -18974,7 +18974,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>554</v>
+        <v>946</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -18994,7 +18994,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>994</v>
+        <v>712</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -19014,7 +19014,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>476</v>
+        <v>713</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -19034,7 +19034,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>557</v>
+        <v>450</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -19054,7 +19054,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>254</v>
+        <v>981</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -19074,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>660</v>
+        <v>856</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -19094,7 +19094,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>476</v>
+        <v>837</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -19114,7 +19114,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>587</v>
+        <v>694</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -19134,7 +19134,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>731</v>
+        <v>690</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -19154,7 +19154,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>683</v>
+        <v>540</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -19174,7 +19174,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>657</v>
+        <v>740</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -19194,7 +19194,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>668</v>
+        <v>938</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -19214,7 +19214,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>537</v>
+        <v>615</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -19234,7 +19234,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>610</v>
+        <v>514</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -19254,7 +19254,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>614</v>
+        <v>726</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -19274,7 +19274,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>588</v>
+        <v>474</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -19294,7 +19294,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>992</v>
+        <v>802</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -19314,7 +19314,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>558</v>
+        <v>825</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -19334,7 +19334,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>738</v>
+        <v>770</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -19354,7 +19354,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>657</v>
+        <v>314</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -19374,7 +19374,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>730</v>
+        <v>676</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -19394,7 +19394,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>675</v>
+        <v>933</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -19414,7 +19414,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>644</v>
+        <v>748</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -19434,7 +19434,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>434</v>
+        <v>324</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -19454,7 +19454,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>401</v>
+        <v>448</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -19474,7 +19474,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>715</v>
+        <v>366</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -19494,7 +19494,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>664</v>
+        <v>283</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -19514,7 +19514,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>491</v>
+        <v>639</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -19534,7 +19534,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>992</v>
+        <v>957</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -19554,7 +19554,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>609</v>
+        <v>279</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -19574,7 +19574,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>571</v>
+        <v>465</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -19594,7 +19594,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>615</v>
+        <v>337</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -19614,7 +19614,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>974</v>
+        <v>506</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -19634,7 +19634,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>641</v>
+        <v>684</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -19654,7 +19654,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>883</v>
+        <v>453</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -19674,7 +19674,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>594</v>
+        <v>382</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -19694,7 +19694,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>340</v>
+        <v>989</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -19714,7 +19714,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>619</v>
+        <v>630</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -19734,7 +19734,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>702</v>
+        <v>314</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -19754,7 +19754,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>914</v>
+        <v>728</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -19774,7 +19774,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>596</v>
+        <v>562</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -19794,7 +19794,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>675</v>
+        <v>406</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -19814,7 +19814,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>727</v>
+        <v>886</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -19834,7 +19834,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>253</v>
+        <v>646</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -19854,7 +19854,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>656</v>
+        <v>502</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -19874,7 +19874,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>572</v>
+        <v>225</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -19894,7 +19894,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>902</v>
+        <v>368</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -19914,7 +19914,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>447</v>
+        <v>710</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -19934,7 +19934,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>484</v>
+        <v>727</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -19954,7 +19954,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>971</v>
+        <v>859</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -19974,7 +19974,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>912</v>
+        <v>546</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -19994,7 +19994,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>312</v>
+        <v>209</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -20014,7 +20014,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>414</v>
+        <v>503</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -20034,7 +20034,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>894</v>
+        <v>727</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -20054,7 +20054,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>776</v>
+        <v>918</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -20074,7 +20074,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>839</v>
+        <v>434</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -20094,7 +20094,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>655</v>
+        <v>448</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -20114,7 +20114,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>646</v>
+        <v>955</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -20134,7 +20134,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>284</v>
+        <v>849</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -20154,7 +20154,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>399</v>
+        <v>741</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -20174,7 +20174,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>323</v>
+        <v>775</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -20194,7 +20194,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>284</v>
+        <v>235</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -20214,7 +20214,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>944</v>
+        <v>244</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -20234,7 +20234,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>798</v>
+        <v>668</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -20254,7 +20254,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>691</v>
+        <v>375</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -20274,7 +20274,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>857</v>
+        <v>651</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -20294,7 +20294,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>429</v>
+        <v>640</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -20314,7 +20314,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>387</v>
+        <v>832</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -20334,7 +20334,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>466</v>
+        <v>705</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -20354,7 +20354,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>824</v>
+        <v>487</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -20374,7 +20374,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -20394,7 +20394,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>320</v>
+        <v>219</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -20414,7 +20414,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>613</v>
+        <v>428</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -20434,7 +20434,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>954</v>
+        <v>374</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -20454,7 +20454,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>830</v>
+        <v>253</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -20474,7 +20474,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>449</v>
+        <v>220</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -20494,7 +20494,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>929</v>
+        <v>451</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -20514,7 +20514,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>393</v>
+        <v>574</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -20534,7 +20534,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>810</v>
+        <v>783</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -20554,7 +20554,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>721</v>
+        <v>343</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -20574,7 +20574,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>231</v>
+        <v>891</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -20594,7 +20594,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>354</v>
+        <v>548</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -20614,7 +20614,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>293</v>
+        <v>688</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -20634,7 +20634,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>479</v>
+        <v>676</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -20654,7 +20654,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>935</v>
+        <v>220</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -20674,7 +20674,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>415</v>
+        <v>245</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -20694,7 +20694,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>892</v>
+        <v>867</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -20714,7 +20714,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>961</v>
+        <v>935</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -20734,7 +20734,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>819</v>
+        <v>595</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -20754,7 +20754,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>981</v>
+        <v>923</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -20774,7 +20774,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>444</v>
+        <v>956</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -20794,7 +20794,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>227</v>
+        <v>316</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -20814,7 +20814,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>570</v>
+        <v>529</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -20834,7 +20834,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>734</v>
+        <v>631</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -20854,7 +20854,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>299</v>
+        <v>946</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -20874,7 +20874,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>303</v>
+        <v>750</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -20894,7 +20894,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>862</v>
+        <v>692</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -20914,7 +20914,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>903</v>
+        <v>802</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -20934,7 +20934,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>901</v>
+        <v>454</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -20954,7 +20954,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>307</v>
+        <v>679</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -20974,7 +20974,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>723</v>
+        <v>233</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -20994,7 +20994,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>308</v>
+        <v>814</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -21014,7 +21014,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>524</v>
+        <v>799</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -21034,7 +21034,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>797</v>
+        <v>511</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -21054,7 +21054,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>689</v>
+        <v>977</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -21074,7 +21074,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>555</v>
+        <v>521</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -21094,7 +21094,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>577</v>
+        <v>827</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -21114,7 +21114,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>738</v>
+        <v>310</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -21134,7 +21134,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>498</v>
+        <v>452</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -21154,7 +21154,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>505</v>
+        <v>667</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -21174,7 +21174,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>632</v>
+        <v>500</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -21194,7 +21194,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>661</v>
+        <v>213</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -21214,7 +21214,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>371</v>
+        <v>735</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -21234,7 +21234,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>568</v>
+        <v>816</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -21254,7 +21254,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>681</v>
+        <v>453</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -21274,7 +21274,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>878</v>
+        <v>907</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -21294,7 +21294,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>274</v>
+        <v>844</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -21314,7 +21314,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>247</v>
+        <v>779</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -21334,7 +21334,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>795</v>
+        <v>317</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -21354,7 +21354,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>207</v>
+        <v>731</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -21374,7 +21374,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>896</v>
+        <v>613</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -21394,7 +21394,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>270</v>
+        <v>743</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -21414,7 +21414,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>748</v>
+        <v>456</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -21434,7 +21434,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>369</v>
+        <v>915</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -21454,7 +21454,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>411</v>
+        <v>741</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -21474,7 +21474,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>856</v>
+        <v>226</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -21494,7 +21494,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>513</v>
+        <v>689</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -21514,7 +21514,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>341</v>
+        <v>894</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -21534,7 +21534,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -21554,7 +21554,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>690</v>
+        <v>834</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -21574,7 +21574,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>840</v>
+        <v>397</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -21594,7 +21594,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>318</v>
+        <v>347</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -21614,7 +21614,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>598</v>
+        <v>506</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -21634,7 +21634,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>541</v>
+        <v>498</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -21654,7 +21654,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>543</v>
+        <v>375</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -21674,7 +21674,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>260</v>
+        <v>224</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -21694,7 +21694,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>292</v>
+        <v>786</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -21714,7 +21714,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>693</v>
+        <v>295</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -21734,7 +21734,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>240</v>
+        <v>952</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -21754,7 +21754,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>649</v>
+        <v>443</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -21774,7 +21774,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>719</v>
+        <v>455</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -21794,7 +21794,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>975</v>
+        <v>305</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -21814,7 +21814,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>926</v>
+        <v>476</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -21834,7 +21834,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>698</v>
+        <v>609</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -21854,7 +21854,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>459</v>
+        <v>873</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -21874,7 +21874,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>849</v>
+        <v>605</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -21894,7 +21894,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>321</v>
+        <v>845</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -21914,7 +21914,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>532</v>
+        <v>722</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -21934,7 +21934,7 @@
         <v>10</v>
       </c>
       <c r="F397">
-        <v>476</v>
+        <v>574</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -21954,7 +21954,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>718</v>
+        <v>705</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -21974,7 +21974,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>873</v>
+        <v>962</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -21994,7 +21994,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>916</v>
+        <v>971</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -22014,7 +22014,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>715</v>
+        <v>276</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -22034,7 +22034,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>233</v>
+        <v>932</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -22054,7 +22054,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>965</v>
+        <v>589</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -22074,7 +22074,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>227</v>
+        <v>201</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -22094,7 +22094,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>539</v>
+        <v>829</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -22114,7 +22114,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>397</v>
+        <v>425</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -22134,7 +22134,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>270</v>
+        <v>721</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -22154,7 +22154,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>821</v>
+        <v>490</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -22174,7 +22174,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>935</v>
+        <v>810</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -22194,7 +22194,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>857</v>
+        <v>706</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -22214,7 +22214,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>335</v>
+        <v>682</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -22234,7 +22234,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>904</v>
+        <v>731</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -22254,7 +22254,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>595</v>
+        <v>575</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -22274,7 +22274,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>304</v>
+        <v>519</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -22294,7 +22294,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>468</v>
+        <v>223</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -22314,7 +22314,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>509</v>
+        <v>890</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -22334,7 +22334,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>603</v>
+        <v>699</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -22354,7 +22354,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>510</v>
+        <v>853</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -22374,7 +22374,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -22394,7 +22394,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>659</v>
+        <v>600</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -22414,7 +22414,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>554</v>
+        <v>475</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -22434,7 +22434,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -22454,7 +22454,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>558</v>
+        <v>426</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -22474,7 +22474,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>213</v>
+        <v>999</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -22494,7 +22494,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>816</v>
+        <v>977</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -22514,7 +22514,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>338</v>
+        <v>355</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -22534,7 +22534,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>834</v>
+        <v>552</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -22554,7 +22554,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>254</v>
+        <v>732</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -22574,7 +22574,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>680</v>
+        <v>862</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -22594,7 +22594,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>616</v>
+        <v>362</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -22614,7 +22614,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>816</v>
+        <v>527</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -22634,7 +22634,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>860</v>
+        <v>988</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -22654,7 +22654,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>307</v>
+        <v>530</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -22674,7 +22674,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>953</v>
+        <v>395</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -22694,7 +22694,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>792</v>
+        <v>440</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -22714,7 +22714,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>936</v>
+        <v>469</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -22734,7 +22734,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>789</v>
+        <v>368</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -22754,7 +22754,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>908</v>
+        <v>747</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -22774,7 +22774,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>685</v>
+        <v>776</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -22794,7 +22794,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>326</v>
+        <v>476</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -22814,7 +22814,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>211</v>
+        <v>250</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -22834,7 +22834,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>867</v>
+        <v>327</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>274</v>
+        <v>589</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -22874,7 +22874,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>408</v>
+        <v>718</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -22894,7 +22894,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>344</v>
+        <v>636</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -22914,7 +22914,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>969</v>
+        <v>477</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -22934,7 +22934,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>722</v>
+        <v>486</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -22954,7 +22954,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>599</v>
+        <v>739</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -22974,7 +22974,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>588</v>
+        <v>924</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>418</v>
+        <v>346</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -23014,7 +23014,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>708</v>
+        <v>528</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -23034,7 +23034,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>314</v>
+        <v>206</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -23054,7 +23054,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>438</v>
+        <v>649</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -23074,7 +23074,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>441</v>
+        <v>245</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -23094,7 +23094,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>333</v>
+        <v>610</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -23114,7 +23114,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>317</v>
+        <v>229</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>947</v>
+        <v>531</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -23154,7 +23154,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>876</v>
+        <v>316</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -23174,7 +23174,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>349</v>
+        <v>784</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -23194,7 +23194,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>529</v>
+        <v>956</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -23214,7 +23214,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>480</v>
+        <v>203</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -23234,7 +23234,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>408</v>
+        <v>347</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -23254,7 +23254,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>885</v>
+        <v>963</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>382</v>
+        <v>579</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -23294,7 +23294,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>266</v>
+        <v>362</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -23314,7 +23314,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>527</v>
+        <v>652</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -23334,7 +23334,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>445</v>
+        <v>357</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -23354,7 +23354,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>648</v>
+        <v>895</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -23374,7 +23374,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>637</v>
+        <v>327</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -23394,7 +23394,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>327</v>
+        <v>750</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>777</v>
+        <v>984</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -23434,7 +23434,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>348</v>
+        <v>994</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -23454,7 +23454,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>852</v>
+        <v>535</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -23474,7 +23474,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>664</v>
+        <v>379</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -23494,7 +23494,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>572</v>
+        <v>995</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -23514,7 +23514,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>936</v>
+        <v>926</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -23534,7 +23534,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>648</v>
+        <v>942</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>996</v>
+        <v>291</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -23574,7 +23574,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>418</v>
+        <v>220</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -23594,7 +23594,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>877</v>
+        <v>851</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -23614,7 +23614,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>283</v>
+        <v>330</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -23634,7 +23634,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>559</v>
+        <v>962</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -23654,7 +23654,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>882</v>
+        <v>202</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -23674,7 +23674,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>579</v>
+        <v>208</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>879</v>
+        <v>924</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -23714,7 +23714,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>899</v>
+        <v>544</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -23734,7 +23734,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>926</v>
+        <v>491</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -23754,7 +23754,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>724</v>
+        <v>473</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -23774,7 +23774,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>898</v>
+        <v>804</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -23794,7 +23794,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>653</v>
+        <v>873</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -23814,7 +23814,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>292</v>
+        <v>379</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>440</v>
+        <v>456</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -23854,7 +23854,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>754</v>
+        <v>257</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -23874,7 +23874,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>998</v>
+        <v>584</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -23894,7 +23894,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>743</v>
+        <v>451</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -23914,7 +23914,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>431</v>
+        <v>399</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -23934,7 +23934,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>818</v>
+        <v>456</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -23954,7 +23954,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>580</v>
+        <v>305</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>364</v>
+        <v>217</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -23994,7 +23994,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>287</v>
+        <v>311</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -24014,7 +24014,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>418</v>
+        <v>447</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -24034,7 +24034,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>238</v>
+        <v>924</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -24054,7 +24054,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>405</v>
+        <v>342</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -24074,7 +24074,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>760</v>
+        <v>865</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -24094,7 +24094,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>405</v>
+        <v>803</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>674</v>
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -24264,7 +24264,7 @@
         <v>622</v>
       </c>
       <c r="F2">
-        <v>527</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -24284,7 +24284,7 @@
         <v>622</v>
       </c>
       <c r="F3">
-        <v>459</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/Excel/Automation_Test_Report.xlsx
@@ -3208,13 +3208,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>BUILD-89</t>
+    <t>BUILD-2026-ENTERPRISE</t>
   </si>
   <si>
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>9/14/2026, 2:58:14 AM</t>
+    <t>30/7/2026, 4:16:52 pm</t>
   </si>
   <si>
     <t>Target Device</t>
@@ -3793,7 +3793,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>611</v>
+        <v>740</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -3813,7 +3813,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>470</v>
+        <v>927</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3833,7 +3833,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>746</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -3853,7 +3853,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>404</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -3873,7 +3873,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>533</v>
+        <v>995</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -3893,7 +3893,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>798</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3913,7 +3913,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>776</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3933,7 +3933,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>461</v>
+        <v>873</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3953,7 +3953,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>926</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3973,7 +3973,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>728</v>
+        <v>947</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3993,7 +3993,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>252</v>
+        <v>672</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4013,7 +4013,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>851</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4033,7 +4033,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>872</v>
+        <v>926</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4053,7 +4053,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>503</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4073,7 +4073,7 @@
         <v>41</v>
       </c>
       <c r="F16">
-        <v>419</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4093,7 +4093,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>294</v>
+        <v>650</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4113,7 +4113,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>928</v>
+        <v>479</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4133,7 +4133,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>380</v>
+        <v>749</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4153,7 +4153,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>203</v>
+        <v>542</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4173,7 +4173,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>303</v>
+        <v>651</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4193,7 +4193,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>836</v>
+        <v>661</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4213,7 +4213,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>709</v>
+        <v>503</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4233,7 +4233,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>415</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -4253,7 +4253,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>244</v>
+        <v>937</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4273,7 +4273,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>882</v>
+        <v>795</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4293,7 +4293,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>605</v>
+        <v>990</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,7 +4313,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>662</v>
+        <v>908</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>569</v>
+        <v>743</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4353,7 +4353,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>735</v>
+        <v>915</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -4373,7 +4373,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>391</v>
+        <v>452</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -4393,7 +4393,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>229</v>
+        <v>619</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -4413,7 +4413,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>937</v>
+        <v>772</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4433,7 +4433,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>761</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4453,7 +4453,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>959</v>
+        <v>694</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4473,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>563</v>
+        <v>757</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4493,7 +4493,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>440</v>
+        <v>746</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4513,7 +4513,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>875</v>
+        <v>752</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -4533,7 +4533,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>319</v>
+        <v>546</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4553,7 +4553,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>717</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4573,7 +4573,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>637</v>
+        <v>496</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -4593,7 +4593,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>374</v>
+        <v>695</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -4613,7 +4613,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>512</v>
+        <v>783</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,7 +4633,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>825</v>
+        <v>465</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -4653,7 +4653,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>324</v>
+        <v>642</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -4673,7 +4673,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>272</v>
+        <v>732</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -4693,7 +4693,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>515</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4713,7 +4713,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>461</v>
+        <v>924</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4733,7 +4733,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>806</v>
+        <v>342</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4753,7 +4753,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4773,7 +4773,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>954</v>
+        <v>469</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4793,7 +4793,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>896</v>
+        <v>692</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4813,7 +4813,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>389</v>
+        <v>732</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4833,7 +4833,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>332</v>
+        <v>865</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4853,7 +4853,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>924</v>
+        <v>784</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4873,7 +4873,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>712</v>
+        <v>690</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4893,7 +4893,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>432</v>
+        <v>332</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4913,7 +4913,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4933,7 +4933,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>931</v>
+        <v>460</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4953,7 +4953,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>503</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4973,7 +4973,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>578</v>
+        <v>754</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4993,7 +4993,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>575</v>
+        <v>245</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -5013,7 +5013,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>490</v>
+        <v>341</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -5033,7 +5033,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>422</v>
+        <v>408</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -5053,7 +5053,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>691</v>
+        <v>943</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -5073,7 +5073,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>480</v>
+        <v>597</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -5093,7 +5093,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>238</v>
+        <v>273</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -5113,7 +5113,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>788</v>
+        <v>858</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5133,7 +5133,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>986</v>
+        <v>485</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -5153,7 +5153,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>713</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -5173,7 +5173,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>263</v>
+        <v>849</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -5193,7 +5193,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>610</v>
+        <v>575</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -5213,7 +5213,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>264</v>
+        <v>801</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -5233,7 +5233,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -5253,7 +5253,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>695</v>
+        <v>573</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -5273,7 +5273,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>291</v>
+        <v>433</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5293,7 +5293,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>956</v>
+        <v>365</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5313,7 +5313,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>339</v>
+        <v>665</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5333,7 +5333,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>679</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5353,7 +5353,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>721</v>
+        <v>911</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5373,7 +5373,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>831</v>
+        <v>936</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5393,7 +5393,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5413,7 +5413,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>885</v>
+        <v>937</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5433,7 +5433,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>484</v>
+        <v>966</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5453,7 +5453,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>391</v>
+        <v>606</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -5473,7 +5473,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>392</v>
+        <v>513</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -5493,7 +5493,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>403</v>
+        <v>786</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -5513,7 +5513,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>991</v>
+        <v>718</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -5533,7 +5533,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>537</v>
+        <v>894</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -5553,7 +5553,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>657</v>
+        <v>999</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -5573,7 +5573,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>864</v>
+        <v>645</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -5593,7 +5593,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>346</v>
+        <v>458</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -5613,7 +5613,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>735</v>
+        <v>378</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -5633,7 +5633,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>801</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -5653,7 +5653,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>488</v>
+        <v>772</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -5673,7 +5673,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>429</v>
+        <v>367</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -5693,7 +5693,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>984</v>
+        <v>823</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -5713,7 +5713,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>892</v>
+        <v>427</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -5733,7 +5733,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>427</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -5753,7 +5753,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>970</v>
+        <v>923</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -5773,7 +5773,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>209</v>
+        <v>448</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -5793,7 +5793,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>762</v>
+        <v>456</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -5813,7 +5813,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>284</v>
+        <v>763</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -5833,7 +5833,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>560</v>
+        <v>785</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -5853,7 +5853,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>300</v>
+        <v>880</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -5873,7 +5873,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>813</v>
+        <v>964</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -5893,7 +5893,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>822</v>
+        <v>629</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -5913,7 +5913,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>472</v>
+        <v>250</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -5933,7 +5933,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>475</v>
+        <v>627</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -5953,7 +5953,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>529</v>
+        <v>426</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -5973,7 +5973,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>733</v>
+        <v>467</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -5993,7 +5993,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>708</v>
+        <v>546</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -6013,7 +6013,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>276</v>
+        <v>202</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -6033,7 +6033,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>670</v>
+        <v>549</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -6053,7 +6053,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>843</v>
+        <v>477</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -6073,7 +6073,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>738</v>
+        <v>968</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -6093,7 +6093,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>468</v>
+        <v>576</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -6113,7 +6113,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>631</v>
+        <v>782</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -6133,7 +6133,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>496</v>
+        <v>729</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -6153,7 +6153,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>780</v>
+        <v>814</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -6173,7 +6173,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>745</v>
+        <v>244</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -6193,7 +6193,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>968</v>
+        <v>828</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -6213,7 +6213,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>899</v>
+        <v>292</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -6233,7 +6233,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>386</v>
+        <v>685</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -6253,7 +6253,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>718</v>
+        <v>419</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -6273,7 +6273,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>340</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -6293,7 +6293,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>968</v>
+        <v>717</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -6313,7 +6313,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>265</v>
+        <v>556</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -6333,7 +6333,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>543</v>
+        <v>934</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -6353,7 +6353,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>729</v>
+        <v>449</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -6373,7 +6373,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>453</v>
+        <v>871</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -6393,7 +6393,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>792</v>
+        <v>382</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -6413,7 +6413,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>533</v>
+        <v>677</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -6433,7 +6433,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>872</v>
+        <v>323</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -6453,7 +6453,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -6473,7 +6473,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>838</v>
+        <v>516</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -6493,7 +6493,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>947</v>
+        <v>677</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -6513,7 +6513,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>712</v>
+        <v>384</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -6533,7 +6533,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>902</v>
+        <v>340</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>702</v>
+        <v>249</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -6573,7 +6573,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>632</v>
+        <v>612</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -6593,7 +6593,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>850</v>
+        <v>800</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -6613,7 +6613,7 @@
         <v>41</v>
       </c>
       <c r="F143">
-        <v>740</v>
+        <v>542</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -6633,7 +6633,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>768</v>
+        <v>359</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -6653,7 +6653,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>345</v>
+        <v>595</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -6673,7 +6673,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>530</v>
+        <v>454</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -6693,7 +6693,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>224</v>
+        <v>914</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -6713,7 +6713,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>677</v>
+        <v>290</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -6733,7 +6733,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>224</v>
+        <v>740</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -6753,7 +6753,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>633</v>
+        <v>468</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -6773,7 +6773,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>977</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -6793,7 +6793,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>741</v>
+        <v>772</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -6813,7 +6813,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>860</v>
+        <v>585</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -6833,7 +6833,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>330</v>
+        <v>795</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -6853,7 +6853,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>977</v>
+        <v>614</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -6873,7 +6873,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>808</v>
+        <v>800</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>930</v>
+        <v>625</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -6913,7 +6913,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>432</v>
+        <v>213</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -6933,7 +6933,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>428</v>
+        <v>359</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -6953,7 +6953,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>965</v>
+        <v>828</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -6973,7 +6973,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>930</v>
+        <v>666</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -6993,7 +6993,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>805</v>
+        <v>696</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -7013,7 +7013,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>652</v>
+        <v>591</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -7033,7 +7033,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>962</v>
+        <v>366</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -7053,7 +7053,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>222</v>
+        <v>678</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -7073,7 +7073,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>462</v>
+        <v>409</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -7093,7 +7093,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>244</v>
+        <v>641</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -7113,7 +7113,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -7133,7 +7133,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>845</v>
+        <v>888</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -7153,7 +7153,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>725</v>
+        <v>659</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -7173,7 +7173,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>305</v>
+        <v>364</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -7193,7 +7193,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -7213,7 +7213,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>427</v>
+        <v>564</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -7233,7 +7233,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>956</v>
+        <v>973</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -7253,7 +7253,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>760</v>
+        <v>884</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -7273,7 +7273,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>350</v>
+        <v>584</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -7293,7 +7293,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>513</v>
+        <v>930</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -7313,7 +7313,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>534</v>
+        <v>872</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -7333,7 +7333,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>470</v>
+        <v>286</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -7353,7 +7353,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>477</v>
+        <v>682</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -7373,7 +7373,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>517</v>
+        <v>277</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -7393,7 +7393,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>598</v>
+        <v>482</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -7413,7 +7413,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>934</v>
+        <v>418</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -7433,7 +7433,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>673</v>
+        <v>243</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -7453,7 +7453,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>831</v>
+        <v>221</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -7473,7 +7473,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>785</v>
+        <v>758</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -7493,7 +7493,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>766</v>
+        <v>745</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -7513,7 +7513,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>479</v>
+        <v>662</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -7533,7 +7533,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>979</v>
+        <v>653</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -7553,7 +7553,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>421</v>
+        <v>657</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>472</v>
+        <v>696</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -7593,7 +7593,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>351</v>
+        <v>206</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -7613,7 +7613,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>482</v>
+        <v>579</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -7633,7 +7633,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>607</v>
+        <v>559</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -7653,7 +7653,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>630</v>
+        <v>777</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -7673,7 +7673,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>639</v>
+        <v>538</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -7693,7 +7693,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>535</v>
+        <v>669</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -7713,7 +7713,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -7733,7 +7733,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>648</v>
+        <v>666</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -7753,7 +7753,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>923</v>
+        <v>539</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -7773,7 +7773,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>771</v>
+        <v>610</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -7793,7 +7793,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>651</v>
+        <v>959</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -7813,7 +7813,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>833</v>
+        <v>219</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -7833,7 +7833,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>916</v>
+        <v>663</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -7853,7 +7853,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>713</v>
+        <v>295</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -7873,7 +7873,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>463</v>
+        <v>730</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -7893,7 +7893,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>650</v>
+        <v>951</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -7913,7 +7913,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>376</v>
+        <v>436</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -7933,7 +7933,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>753</v>
+        <v>904</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -7953,7 +7953,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>801</v>
+        <v>833</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -7973,7 +7973,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>674</v>
+        <v>889</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -7993,7 +7993,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>864</v>
+        <v>401</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -8013,7 +8013,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>900</v>
+        <v>716</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -8033,7 +8033,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>447</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -8053,7 +8053,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>595</v>
+        <v>325</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -8073,7 +8073,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>654</v>
+        <v>862</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -8093,7 +8093,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>334</v>
+        <v>992</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -8113,7 +8113,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>913</v>
+        <v>835</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -8133,7 +8133,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>483</v>
+        <v>876</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -8153,7 +8153,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>805</v>
+        <v>471</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -8173,7 +8173,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>341</v>
+        <v>729</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -8193,7 +8193,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>354</v>
+        <v>297</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -8213,7 +8213,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>780</v>
+        <v>510</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -8233,7 +8233,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>802</v>
+        <v>512</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -8253,7 +8253,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>201</v>
+        <v>267</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -8273,7 +8273,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>658</v>
+        <v>979</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -8293,7 +8293,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>264</v>
+        <v>951</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -8313,7 +8313,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>834</v>
+        <v>396</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -8333,7 +8333,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>881</v>
+        <v>858</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -8353,7 +8353,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>475</v>
+        <v>239</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -8373,7 +8373,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>467</v>
+        <v>379</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -8393,7 +8393,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>630</v>
+        <v>541</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -8413,7 +8413,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>696</v>
+        <v>370</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -8433,7 +8433,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>296</v>
+        <v>938</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -8453,7 +8453,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>677</v>
+        <v>801</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -8473,7 +8473,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>933</v>
+        <v>583</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -8493,7 +8493,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>827</v>
+        <v>452</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -8513,7 +8513,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>753</v>
+        <v>943</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -8533,7 +8533,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>531</v>
+        <v>289</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -8553,7 +8553,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>311</v>
+        <v>390</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -8573,7 +8573,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>264</v>
+        <v>963</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -8593,7 +8593,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>485</v>
+        <v>930</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -8613,7 +8613,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>915</v>
+        <v>904</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -8633,7 +8633,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>228</v>
+        <v>783</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -8653,7 +8653,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>299</v>
+        <v>362</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -8673,7 +8673,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>593</v>
+        <v>659</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -8693,7 +8693,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>480</v>
+        <v>612</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -8713,7 +8713,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>462</v>
+        <v>851</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -8733,7 +8733,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>590</v>
+        <v>355</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -8753,7 +8753,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>381</v>
+        <v>868</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -8773,7 +8773,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>946</v>
+        <v>837</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -8793,7 +8793,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>712</v>
+        <v>386</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -8813,7 +8813,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>713</v>
+        <v>337</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -8833,7 +8833,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>450</v>
+        <v>676</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -8853,7 +8853,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>981</v>
+        <v>464</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -8873,7 +8873,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>856</v>
+        <v>938</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -8893,7 +8893,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>837</v>
+        <v>658</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -8913,7 +8913,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>694</v>
+        <v>397</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -8933,7 +8933,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>690</v>
+        <v>358</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -8953,7 +8953,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>540</v>
+        <v>377</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -8973,7 +8973,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>740</v>
+        <v>909</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -8993,7 +8993,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>938</v>
+        <v>502</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -9013,7 +9013,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>615</v>
+        <v>338</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -9033,7 +9033,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>514</v>
+        <v>958</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -9053,7 +9053,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>726</v>
+        <v>645</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -9073,7 +9073,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>474</v>
+        <v>712</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -9093,7 +9093,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>802</v>
+        <v>701</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -9113,7 +9113,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>825</v>
+        <v>842</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -9133,7 +9133,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>770</v>
+        <v>800</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -9153,7 +9153,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>314</v>
+        <v>267</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -9173,7 +9173,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>676</v>
+        <v>981</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -9193,7 +9193,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>933</v>
+        <v>575</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -9213,7 +9213,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>748</v>
+        <v>936</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -9233,7 +9233,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>324</v>
+        <v>984</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -9253,7 +9253,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>448</v>
+        <v>943</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -9273,7 +9273,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>366</v>
+        <v>800</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -9293,7 +9293,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>283</v>
+        <v>434</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -9313,7 +9313,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>639</v>
+        <v>411</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -9333,7 +9333,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>957</v>
+        <v>922</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -9353,7 +9353,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>279</v>
+        <v>460</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -9373,7 +9373,7 @@
         <v>41</v>
       </c>
       <c r="F281">
-        <v>520</v>
+        <v>459</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -9393,7 +9393,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>465</v>
+        <v>297</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -9413,7 +9413,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>337</v>
+        <v>501</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -9433,7 +9433,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>506</v>
+        <v>488</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -9453,7 +9453,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>684</v>
+        <v>837</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -9473,7 +9473,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>453</v>
+        <v>318</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -9493,7 +9493,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>382</v>
+        <v>284</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -9513,7 +9513,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>989</v>
+        <v>806</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -9533,7 +9533,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>630</v>
+        <v>319</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -9553,7 +9553,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>314</v>
+        <v>576</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -9573,7 +9573,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>728</v>
+        <v>656</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -9593,7 +9593,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>562</v>
+        <v>207</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -9613,7 +9613,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>406</v>
+        <v>233</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -9633,7 +9633,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>886</v>
+        <v>688</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -9653,7 +9653,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>646</v>
+        <v>296</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -9673,7 +9673,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>502</v>
+        <v>414</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -9693,7 +9693,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>225</v>
+        <v>704</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -9713,7 +9713,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>368</v>
+        <v>694</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -9733,7 +9733,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>710</v>
+        <v>378</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -9753,7 +9753,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>727</v>
+        <v>950</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -9773,7 +9773,7 @@
         <v>622</v>
       </c>
       <c r="F301">
-        <v>333</v>
+        <v>222</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -9793,7 +9793,7 @@
         <v>622</v>
       </c>
       <c r="F302">
-        <v>557</v>
+        <v>958</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -9813,7 +9813,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>859</v>
+        <v>902</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -9833,7 +9833,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>546</v>
+        <v>789</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -9853,7 +9853,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>209</v>
+        <v>766</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -9873,7 +9873,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>503</v>
+        <v>971</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -9893,7 +9893,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>727</v>
+        <v>425</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -9913,7 +9913,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>918</v>
+        <v>900</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -9933,7 +9933,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>434</v>
+        <v>968</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>448</v>
+        <v>470</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -9973,7 +9973,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>955</v>
+        <v>247</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -9993,7 +9993,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>849</v>
+        <v>986</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -10013,7 +10013,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>741</v>
+        <v>505</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -10033,7 +10033,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>775</v>
+        <v>749</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -10053,7 +10053,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>235</v>
+        <v>825</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -10073,7 +10073,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>244</v>
+        <v>902</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -10093,7 +10093,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>668</v>
+        <v>732</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -10113,7 +10113,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>375</v>
+        <v>830</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -10133,7 +10133,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>651</v>
+        <v>606</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -10153,7 +10153,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>640</v>
+        <v>212</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -10173,7 +10173,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>832</v>
+        <v>961</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -10193,7 +10193,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>705</v>
+        <v>304</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -10213,7 +10213,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>487</v>
+        <v>854</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -10233,7 +10233,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>305</v>
+        <v>893</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -10253,7 +10253,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>219</v>
+        <v>736</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -10273,7 +10273,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>428</v>
+        <v>517</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -10293,7 +10293,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>374</v>
+        <v>794</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -10313,7 +10313,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>253</v>
+        <v>319</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -10333,7 +10333,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>220</v>
+        <v>669</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -10353,7 +10353,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>451</v>
+        <v>611</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -10373,7 +10373,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>574</v>
+        <v>363</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -10393,7 +10393,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>783</v>
+        <v>238</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -10413,7 +10413,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>343</v>
+        <v>551</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -10433,7 +10433,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>891</v>
+        <v>410</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -10453,7 +10453,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>548</v>
+        <v>872</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -10473,7 +10473,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>688</v>
+        <v>383</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -10493,7 +10493,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>676</v>
+        <v>362</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -10513,7 +10513,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>220</v>
+        <v>374</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -10533,7 +10533,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -10553,7 +10553,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>867</v>
+        <v>305</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -10573,7 +10573,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>935</v>
+        <v>670</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -10593,7 +10593,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>595</v>
+        <v>611</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -10613,7 +10613,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>923</v>
+        <v>734</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -10633,7 +10633,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>956</v>
+        <v>300</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -10653,7 +10653,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>316</v>
+        <v>413</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -10673,7 +10673,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>529</v>
+        <v>519</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -10693,7 +10693,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>631</v>
+        <v>260</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -10713,7 +10713,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>946</v>
+        <v>922</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -10733,7 +10733,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -10753,7 +10753,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>692</v>
+        <v>832</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -10773,7 +10773,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>802</v>
+        <v>652</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -10793,7 +10793,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>454</v>
+        <v>414</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -10813,7 +10813,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>679</v>
+        <v>977</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -10833,7 +10833,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>233</v>
+        <v>845</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -10853,7 +10853,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>814</v>
+        <v>430</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -10873,7 +10873,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>799</v>
+        <v>227</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -10893,7 +10893,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>511</v>
+        <v>746</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -10913,7 +10913,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>977</v>
+        <v>910</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -10933,7 +10933,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>521</v>
+        <v>416</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -10953,7 +10953,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>827</v>
+        <v>757</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -10973,7 +10973,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>310</v>
+        <v>270</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -10993,7 +10993,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>452</v>
+        <v>586</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -11013,7 +11013,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>667</v>
+        <v>583</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -11033,7 +11033,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>500</v>
+        <v>545</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -11053,7 +11053,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>213</v>
+        <v>618</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -11073,7 +11073,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>735</v>
+        <v>294</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -11093,7 +11093,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>816</v>
+        <v>563</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -11113,7 +11113,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>453</v>
+        <v>420</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -11133,7 +11133,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>907</v>
+        <v>688</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -11153,7 +11153,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>844</v>
+        <v>453</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -11173,7 +11173,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -11193,7 +11193,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>317</v>
+        <v>236</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -11213,7 +11213,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>731</v>
+        <v>830</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -11233,7 +11233,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>613</v>
+        <v>648</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -11253,7 +11253,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>743</v>
+        <v>720</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -11273,7 +11273,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>456</v>
+        <v>374</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -11293,7 +11293,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>915</v>
+        <v>633</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>741</v>
+        <v>252</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -11333,7 +11333,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>226</v>
+        <v>922</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -11353,7 +11353,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>689</v>
+        <v>605</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -11373,7 +11373,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>894</v>
+        <v>473</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -11393,7 +11393,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>263</v>
+        <v>415</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -11413,7 +11413,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>834</v>
+        <v>251</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -11433,7 +11433,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>397</v>
+        <v>951</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -11453,7 +11453,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>347</v>
+        <v>946</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -11473,7 +11473,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>506</v>
+        <v>820</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -11493,7 +11493,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>498</v>
+        <v>985</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -11513,7 +11513,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>375</v>
+        <v>795</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -11533,7 +11533,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>224</v>
+        <v>449</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -11553,7 +11553,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>786</v>
+        <v>452</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -11573,7 +11573,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>295</v>
+        <v>624</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -11593,7 +11593,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>952</v>
+        <v>475</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -11613,7 +11613,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>443</v>
+        <v>407</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -11633,7 +11633,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>455</v>
+        <v>609</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -11653,7 +11653,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>305</v>
+        <v>832</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -11673,7 +11673,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>476</v>
+        <v>924</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -11693,7 +11693,7 @@
         <v>10</v>
       </c>
       <c r="F397">
-        <v>609</v>
+        <v>464</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -11713,7 +11713,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>873</v>
+        <v>538</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -11733,7 +11733,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>605</v>
+        <v>466</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -11753,7 +11753,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>845</v>
+        <v>257</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -11773,7 +11773,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>722</v>
+        <v>652</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -11793,7 +11793,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>574</v>
+        <v>426</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -11813,7 +11813,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>705</v>
+        <v>671</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -11833,7 +11833,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>962</v>
+        <v>414</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -11853,7 +11853,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>971</v>
+        <v>312</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -11873,7 +11873,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>276</v>
+        <v>658</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -11893,7 +11893,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>932</v>
+        <v>340</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -11913,7 +11913,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>589</v>
+        <v>879</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -11933,7 +11933,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>201</v>
+        <v>365</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -11953,7 +11953,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>829</v>
+        <v>909</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -11973,7 +11973,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>425</v>
+        <v>804</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -11993,7 +11993,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>721</v>
+        <v>966</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -12013,7 +12013,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>490</v>
+        <v>962</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -12033,7 +12033,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>810</v>
+        <v>254</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -12053,7 +12053,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>706</v>
+        <v>291</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -12073,7 +12073,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>682</v>
+        <v>584</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -12093,7 +12093,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>731</v>
+        <v>460</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -12113,7 +12113,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>575</v>
+        <v>231</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -12133,7 +12133,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>519</v>
+        <v>608</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -12153,7 +12153,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>223</v>
+        <v>421</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -12173,7 +12173,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>890</v>
+        <v>906</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -12193,7 +12193,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>699</v>
+        <v>399</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -12213,7 +12213,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>853</v>
+        <v>896</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -12233,7 +12233,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>430</v>
+        <v>245</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -12253,7 +12253,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>600</v>
+        <v>733</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -12273,7 +12273,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>475</v>
+        <v>917</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -12293,7 +12293,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>553</v>
+        <v>819</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -12313,7 +12313,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>426</v>
+        <v>400</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>999</v>
+        <v>812</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -12353,7 +12353,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>977</v>
+        <v>410</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -12373,7 +12373,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>355</v>
+        <v>336</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -12393,7 +12393,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>552</v>
+        <v>859</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -12413,7 +12413,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>732</v>
+        <v>467</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -12433,7 +12433,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>862</v>
+        <v>234</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -12453,7 +12453,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>362</v>
+        <v>432</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -12473,7 +12473,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>527</v>
+        <v>872</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -12493,7 +12493,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>988</v>
+        <v>252</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -12513,7 +12513,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>530</v>
+        <v>898</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -12533,7 +12533,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>395</v>
+        <v>694</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -12553,7 +12553,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>440</v>
+        <v>639</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -12573,7 +12573,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>469</v>
+        <v>521</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -12593,7 +12593,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>368</v>
+        <v>917</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -12613,7 +12613,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>747</v>
+        <v>718</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -12633,7 +12633,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>776</v>
+        <v>654</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -12653,7 +12653,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>476</v>
+        <v>719</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -12673,7 +12673,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>250</v>
+        <v>465</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -12693,7 +12693,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>327</v>
+        <v>937</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -12713,7 +12713,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>589</v>
+        <v>688</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -12753,7 +12753,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>636</v>
+        <v>562</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -12773,7 +12773,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>477</v>
+        <v>225</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -12793,7 +12793,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>486</v>
+        <v>981</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -12813,7 +12813,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>739</v>
+        <v>758</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -12833,7 +12833,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>924</v>
+        <v>843</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -12853,7 +12853,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>346</v>
+        <v>902</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -12873,7 +12873,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>528</v>
+        <v>445</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -12893,7 +12893,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>206</v>
+        <v>638</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -12913,7 +12913,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>649</v>
+        <v>763</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -12933,7 +12933,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>245</v>
+        <v>561</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -12953,7 +12953,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>610</v>
+        <v>989</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -12973,7 +12973,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>229</v>
+        <v>912</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -12993,7 +12993,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>531</v>
+        <v>418</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -13013,7 +13013,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>316</v>
+        <v>676</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -13033,7 +13033,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>784</v>
+        <v>608</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -13053,7 +13053,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>956</v>
+        <v>633</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -13073,7 +13073,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -13093,7 +13093,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>347</v>
+        <v>288</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -13113,7 +13113,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>963</v>
+        <v>589</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -13133,7 +13133,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>579</v>
+        <v>431</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -13153,7 +13153,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>362</v>
+        <v>309</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -13173,7 +13173,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>652</v>
+        <v>589</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -13193,7 +13193,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>357</v>
+        <v>637</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -13213,7 +13213,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>895</v>
+        <v>786</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -13233,7 +13233,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>327</v>
+        <v>827</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -13253,7 +13253,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>750</v>
+        <v>510</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -13273,7 +13273,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>984</v>
+        <v>743</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -13293,7 +13293,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>994</v>
+        <v>666</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -13313,7 +13313,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>535</v>
+        <v>723</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -13333,7 +13333,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>379</v>
+        <v>857</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -13353,7 +13353,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>995</v>
+        <v>454</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -13373,7 +13373,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>926</v>
+        <v>879</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -13393,7 +13393,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>942</v>
+        <v>257</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -13413,7 +13413,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>291</v>
+        <v>780</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -13433,7 +13433,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>220</v>
+        <v>726</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -13453,7 +13453,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>851</v>
+        <v>698</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -13473,7 +13473,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>330</v>
+        <v>880</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -13493,7 +13493,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>962</v>
+        <v>913</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -13513,7 +13513,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>202</v>
+        <v>852</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -13533,7 +13533,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>208</v>
+        <v>945</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -13553,7 +13553,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>924</v>
+        <v>270</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -13573,7 +13573,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>544</v>
+        <v>279</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -13593,7 +13593,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>491</v>
+        <v>885</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -13613,7 +13613,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>473</v>
+        <v>374</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -13633,7 +13633,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>804</v>
+        <v>782</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -13653,7 +13653,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>873</v>
+        <v>219</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -13673,7 +13673,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>379</v>
+        <v>417</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -13693,7 +13693,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>456</v>
+        <v>586</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -13713,7 +13713,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>257</v>
+        <v>200</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -13733,7 +13733,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>584</v>
+        <v>855</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -13753,7 +13753,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>451</v>
+        <v>745</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -13773,7 +13773,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>399</v>
+        <v>767</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -13793,7 +13793,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>456</v>
+        <v>530</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -13813,7 +13813,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>305</v>
+        <v>553</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -13833,7 +13833,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>217</v>
+        <v>442</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -13853,7 +13853,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>311</v>
+        <v>200</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -13873,7 +13873,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>447</v>
+        <v>757</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
@@ -13893,7 +13893,7 @@
         <v>10</v>
       </c>
       <c r="F507">
-        <v>924</v>
+        <v>893</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -13913,7 +13913,7 @@
         <v>10</v>
       </c>
       <c r="F508">
-        <v>342</v>
+        <v>997</v>
       </c>
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
@@ -13933,7 +13933,7 @@
         <v>10</v>
       </c>
       <c r="F509">
-        <v>865</v>
+        <v>426</v>
       </c>
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
@@ -13953,7 +13953,7 @@
         <v>10</v>
       </c>
       <c r="F510">
-        <v>803</v>
+        <v>993</v>
       </c>
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
@@ -13973,7 +13973,7 @@
         <v>10</v>
       </c>
       <c r="F511">
-        <v>759</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -14034,7 +14034,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>611</v>
+        <v>740</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -14054,7 +14054,7 @@
         <v>10</v>
       </c>
       <c r="F3">
-        <v>470</v>
+        <v>927</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -14074,7 +14074,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>746</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -14094,7 +14094,7 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>404</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -14114,7 +14114,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>533</v>
+        <v>995</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -14134,7 +14134,7 @@
         <v>10</v>
       </c>
       <c r="F7">
-        <v>798</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -14154,7 +14154,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>776</v>
+        <v>704</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -14174,7 +14174,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>461</v>
+        <v>873</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -14194,7 +14194,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>926</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -14214,7 +14214,7 @@
         <v>10</v>
       </c>
       <c r="F11">
-        <v>728</v>
+        <v>947</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -14234,7 +14234,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>252</v>
+        <v>672</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -14254,7 +14254,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>851</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -14274,7 +14274,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>872</v>
+        <v>926</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -14294,7 +14294,7 @@
         <v>10</v>
       </c>
       <c r="F15">
-        <v>503</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -14314,7 +14314,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>294</v>
+        <v>650</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -14334,7 +14334,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>928</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -14354,7 +14354,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>380</v>
+        <v>749</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -14374,7 +14374,7 @@
         <v>10</v>
       </c>
       <c r="F19">
-        <v>203</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -14394,7 +14394,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>303</v>
+        <v>651</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -14414,7 +14414,7 @@
         <v>10</v>
       </c>
       <c r="F21">
-        <v>836</v>
+        <v>661</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -14434,7 +14434,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>709</v>
+        <v>503</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -14454,7 +14454,7 @@
         <v>10</v>
       </c>
       <c r="F23">
-        <v>415</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -14474,7 +14474,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>244</v>
+        <v>937</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -14494,7 +14494,7 @@
         <v>10</v>
       </c>
       <c r="F25">
-        <v>882</v>
+        <v>795</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -14514,7 +14514,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>605</v>
+        <v>990</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -14534,7 +14534,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>662</v>
+        <v>908</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -14554,7 +14554,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>569</v>
+        <v>743</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -14574,7 +14574,7 @@
         <v>10</v>
       </c>
       <c r="F29">
-        <v>735</v>
+        <v>915</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -14594,7 +14594,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>391</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -14614,7 +14614,7 @@
         <v>10</v>
       </c>
       <c r="F31">
-        <v>229</v>
+        <v>619</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -14634,7 +14634,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>937</v>
+        <v>772</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -14654,7 +14654,7 @@
         <v>10</v>
       </c>
       <c r="F33">
-        <v>761</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -14674,7 +14674,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>959</v>
+        <v>694</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -14694,7 +14694,7 @@
         <v>10</v>
       </c>
       <c r="F35">
-        <v>563</v>
+        <v>757</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -14714,7 +14714,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>440</v>
+        <v>746</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -14734,7 +14734,7 @@
         <v>10</v>
       </c>
       <c r="F37">
-        <v>875</v>
+        <v>752</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -14754,7 +14754,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>319</v>
+        <v>546</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -14774,7 +14774,7 @@
         <v>10</v>
       </c>
       <c r="F39">
-        <v>717</v>
+        <v>450</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -14794,7 +14794,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>637</v>
+        <v>496</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -14814,7 +14814,7 @@
         <v>10</v>
       </c>
       <c r="F41">
-        <v>374</v>
+        <v>695</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -14834,7 +14834,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>512</v>
+        <v>783</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -14854,7 +14854,7 @@
         <v>10</v>
       </c>
       <c r="F43">
-        <v>825</v>
+        <v>465</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -14874,7 +14874,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>324</v>
+        <v>642</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -14894,7 +14894,7 @@
         <v>10</v>
       </c>
       <c r="F45">
-        <v>272</v>
+        <v>732</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -14914,7 +14914,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>515</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -14934,7 +14934,7 @@
         <v>10</v>
       </c>
       <c r="F47">
-        <v>461</v>
+        <v>924</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -14954,7 +14954,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>806</v>
+        <v>342</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -14974,7 +14974,7 @@
         <v>10</v>
       </c>
       <c r="F49">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -14994,7 +14994,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>954</v>
+        <v>469</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -15014,7 +15014,7 @@
         <v>10</v>
       </c>
       <c r="F51">
-        <v>896</v>
+        <v>692</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -15034,7 +15034,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>389</v>
+        <v>732</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -15054,7 +15054,7 @@
         <v>10</v>
       </c>
       <c r="F53">
-        <v>332</v>
+        <v>865</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -15074,7 +15074,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>924</v>
+        <v>784</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -15094,7 +15094,7 @@
         <v>10</v>
       </c>
       <c r="F55">
-        <v>712</v>
+        <v>690</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -15114,7 +15114,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>432</v>
+        <v>332</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -15134,7 +15134,7 @@
         <v>10</v>
       </c>
       <c r="F57">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -15154,7 +15154,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>931</v>
+        <v>460</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -15174,7 +15174,7 @@
         <v>10</v>
       </c>
       <c r="F59">
-        <v>503</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -15194,7 +15194,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>578</v>
+        <v>754</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -15214,7 +15214,7 @@
         <v>10</v>
       </c>
       <c r="F61">
-        <v>575</v>
+        <v>245</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -15234,7 +15234,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>490</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -15254,7 +15254,7 @@
         <v>10</v>
       </c>
       <c r="F63">
-        <v>422</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -15274,7 +15274,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>691</v>
+        <v>943</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -15294,7 +15294,7 @@
         <v>10</v>
       </c>
       <c r="F65">
-        <v>480</v>
+        <v>597</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -15314,7 +15314,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>238</v>
+        <v>273</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -15334,7 +15334,7 @@
         <v>10</v>
       </c>
       <c r="F67">
-        <v>788</v>
+        <v>858</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -15354,7 +15354,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>986</v>
+        <v>485</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -15374,7 +15374,7 @@
         <v>10</v>
       </c>
       <c r="F69">
-        <v>713</v>
+        <v>324</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -15394,7 +15394,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>263</v>
+        <v>849</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -15414,7 +15414,7 @@
         <v>10</v>
       </c>
       <c r="F71">
-        <v>610</v>
+        <v>575</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -15434,7 +15434,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>264</v>
+        <v>801</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -15454,7 +15454,7 @@
         <v>10</v>
       </c>
       <c r="F73">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -15474,7 +15474,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>695</v>
+        <v>573</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -15494,7 +15494,7 @@
         <v>10</v>
       </c>
       <c r="F75">
-        <v>291</v>
+        <v>433</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -15514,7 +15514,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>956</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -15534,7 +15534,7 @@
         <v>10</v>
       </c>
       <c r="F77">
-        <v>339</v>
+        <v>665</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -15554,7 +15554,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>679</v>
+        <v>309</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -15574,7 +15574,7 @@
         <v>10</v>
       </c>
       <c r="F79">
-        <v>721</v>
+        <v>911</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -15594,7 +15594,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>831</v>
+        <v>936</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -15614,7 +15614,7 @@
         <v>10</v>
       </c>
       <c r="F81">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -15634,7 +15634,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>885</v>
+        <v>937</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -15654,7 +15654,7 @@
         <v>10</v>
       </c>
       <c r="F83">
-        <v>484</v>
+        <v>966</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -15674,7 +15674,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>391</v>
+        <v>606</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -15694,7 +15694,7 @@
         <v>10</v>
       </c>
       <c r="F85">
-        <v>392</v>
+        <v>513</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -15714,7 +15714,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>403</v>
+        <v>786</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -15734,7 +15734,7 @@
         <v>10</v>
       </c>
       <c r="F87">
-        <v>991</v>
+        <v>718</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -15754,7 +15754,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>537</v>
+        <v>894</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -15774,7 +15774,7 @@
         <v>10</v>
       </c>
       <c r="F89">
-        <v>657</v>
+        <v>999</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -15794,7 +15794,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>864</v>
+        <v>645</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -15814,7 +15814,7 @@
         <v>10</v>
       </c>
       <c r="F91">
-        <v>346</v>
+        <v>458</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -15834,7 +15834,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>735</v>
+        <v>378</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -15854,7 +15854,7 @@
         <v>10</v>
       </c>
       <c r="F93">
-        <v>801</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -15874,7 +15874,7 @@
         <v>10</v>
       </c>
       <c r="F94">
-        <v>488</v>
+        <v>772</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -15894,7 +15894,7 @@
         <v>10</v>
       </c>
       <c r="F95">
-        <v>429</v>
+        <v>367</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -15914,7 +15914,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>984</v>
+        <v>823</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -15934,7 +15934,7 @@
         <v>10</v>
       </c>
       <c r="F97">
-        <v>892</v>
+        <v>427</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -15954,7 +15954,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>427</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -15974,7 +15974,7 @@
         <v>10</v>
       </c>
       <c r="F99">
-        <v>970</v>
+        <v>923</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -15994,7 +15994,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>209</v>
+        <v>448</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -16014,7 +16014,7 @@
         <v>10</v>
       </c>
       <c r="F101">
-        <v>762</v>
+        <v>456</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -16034,7 +16034,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>284</v>
+        <v>763</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -16054,7 +16054,7 @@
         <v>10</v>
       </c>
       <c r="F103">
-        <v>560</v>
+        <v>785</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -16074,7 +16074,7 @@
         <v>10</v>
       </c>
       <c r="F104">
-        <v>300</v>
+        <v>880</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -16094,7 +16094,7 @@
         <v>10</v>
       </c>
       <c r="F105">
-        <v>813</v>
+        <v>964</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -16114,7 +16114,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>822</v>
+        <v>629</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -16134,7 +16134,7 @@
         <v>10</v>
       </c>
       <c r="F107">
-        <v>472</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -16154,7 +16154,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>475</v>
+        <v>627</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -16174,7 +16174,7 @@
         <v>10</v>
       </c>
       <c r="F109">
-        <v>529</v>
+        <v>426</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -16194,7 +16194,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>733</v>
+        <v>467</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -16214,7 +16214,7 @@
         <v>10</v>
       </c>
       <c r="F111">
-        <v>708</v>
+        <v>546</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -16234,7 +16234,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>276</v>
+        <v>202</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -16254,7 +16254,7 @@
         <v>10</v>
       </c>
       <c r="F113">
-        <v>670</v>
+        <v>549</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -16274,7 +16274,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>843</v>
+        <v>477</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -16294,7 +16294,7 @@
         <v>10</v>
       </c>
       <c r="F115">
-        <v>738</v>
+        <v>968</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -16314,7 +16314,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>468</v>
+        <v>576</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -16334,7 +16334,7 @@
         <v>10</v>
       </c>
       <c r="F117">
-        <v>631</v>
+        <v>782</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -16354,7 +16354,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>496</v>
+        <v>729</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -16374,7 +16374,7 @@
         <v>10</v>
       </c>
       <c r="F119">
-        <v>780</v>
+        <v>814</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -16394,7 +16394,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>745</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -16414,7 +16414,7 @@
         <v>10</v>
       </c>
       <c r="F121">
-        <v>968</v>
+        <v>828</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -16434,7 +16434,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>899</v>
+        <v>292</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -16454,7 +16454,7 @@
         <v>10</v>
       </c>
       <c r="F123">
-        <v>386</v>
+        <v>685</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -16474,7 +16474,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>718</v>
+        <v>419</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -16494,7 +16494,7 @@
         <v>10</v>
       </c>
       <c r="F125">
-        <v>340</v>
+        <v>269</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -16514,7 +16514,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>968</v>
+        <v>717</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -16534,7 +16534,7 @@
         <v>10</v>
       </c>
       <c r="F127">
-        <v>265</v>
+        <v>556</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -16554,7 +16554,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>543</v>
+        <v>934</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -16574,7 +16574,7 @@
         <v>10</v>
       </c>
       <c r="F129">
-        <v>729</v>
+        <v>449</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -16594,7 +16594,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>453</v>
+        <v>871</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -16614,7 +16614,7 @@
         <v>10</v>
       </c>
       <c r="F131">
-        <v>792</v>
+        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -16634,7 +16634,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>533</v>
+        <v>677</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -16654,7 +16654,7 @@
         <v>10</v>
       </c>
       <c r="F133">
-        <v>872</v>
+        <v>323</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -16674,7 +16674,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>295</v>
+        <v>313</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -16694,7 +16694,7 @@
         <v>10</v>
       </c>
       <c r="F135">
-        <v>838</v>
+        <v>516</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -16714,7 +16714,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>947</v>
+        <v>677</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -16734,7 +16734,7 @@
         <v>10</v>
       </c>
       <c r="F137">
-        <v>712</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -16754,7 +16754,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>902</v>
+        <v>340</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -16774,7 +16774,7 @@
         <v>10</v>
       </c>
       <c r="F139">
-        <v>702</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -16794,7 +16794,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>632</v>
+        <v>612</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -16814,7 +16814,7 @@
         <v>10</v>
       </c>
       <c r="F141">
-        <v>850</v>
+        <v>800</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -16834,7 +16834,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>768</v>
+        <v>359</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -16854,7 +16854,7 @@
         <v>10</v>
       </c>
       <c r="F143">
-        <v>345</v>
+        <v>595</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -16874,7 +16874,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>530</v>
+        <v>454</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -16894,7 +16894,7 @@
         <v>10</v>
       </c>
       <c r="F145">
-        <v>224</v>
+        <v>914</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -16914,7 +16914,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>677</v>
+        <v>290</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -16934,7 +16934,7 @@
         <v>10</v>
       </c>
       <c r="F147">
-        <v>224</v>
+        <v>740</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -16954,7 +16954,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>633</v>
+        <v>468</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -16974,7 +16974,7 @@
         <v>10</v>
       </c>
       <c r="F149">
-        <v>977</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -16994,7 +16994,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>741</v>
+        <v>772</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -17014,7 +17014,7 @@
         <v>10</v>
       </c>
       <c r="F151">
-        <v>860</v>
+        <v>585</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -17034,7 +17034,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>330</v>
+        <v>795</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -17054,7 +17054,7 @@
         <v>10</v>
       </c>
       <c r="F153">
-        <v>977</v>
+        <v>614</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -17074,7 +17074,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>808</v>
+        <v>800</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -17094,7 +17094,7 @@
         <v>10</v>
       </c>
       <c r="F155">
-        <v>930</v>
+        <v>625</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -17114,7 +17114,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>432</v>
+        <v>213</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -17134,7 +17134,7 @@
         <v>10</v>
       </c>
       <c r="F157">
-        <v>428</v>
+        <v>359</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -17154,7 +17154,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>965</v>
+        <v>828</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -17174,7 +17174,7 @@
         <v>10</v>
       </c>
       <c r="F159">
-        <v>930</v>
+        <v>666</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -17194,7 +17194,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>805</v>
+        <v>696</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -17214,7 +17214,7 @@
         <v>10</v>
       </c>
       <c r="F161">
-        <v>652</v>
+        <v>591</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -17234,7 +17234,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>962</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -17254,7 +17254,7 @@
         <v>10</v>
       </c>
       <c r="F163">
-        <v>222</v>
+        <v>678</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -17274,7 +17274,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>462</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -17294,7 +17294,7 @@
         <v>10</v>
       </c>
       <c r="F165">
-        <v>244</v>
+        <v>641</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -17314,7 +17314,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -17334,7 +17334,7 @@
         <v>10</v>
       </c>
       <c r="F167">
-        <v>845</v>
+        <v>888</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -17354,7 +17354,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>725</v>
+        <v>659</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -17374,7 +17374,7 @@
         <v>10</v>
       </c>
       <c r="F169">
-        <v>305</v>
+        <v>364</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -17394,7 +17394,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -17414,7 +17414,7 @@
         <v>10</v>
       </c>
       <c r="F171">
-        <v>427</v>
+        <v>564</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -17434,7 +17434,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>956</v>
+        <v>973</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -17454,7 +17454,7 @@
         <v>10</v>
       </c>
       <c r="F173">
-        <v>760</v>
+        <v>884</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -17474,7 +17474,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>350</v>
+        <v>584</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -17494,7 +17494,7 @@
         <v>10</v>
       </c>
       <c r="F175">
-        <v>513</v>
+        <v>930</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -17514,7 +17514,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>534</v>
+        <v>872</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -17534,7 +17534,7 @@
         <v>10</v>
       </c>
       <c r="F177">
-        <v>470</v>
+        <v>286</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -17554,7 +17554,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>477</v>
+        <v>682</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -17574,7 +17574,7 @@
         <v>10</v>
       </c>
       <c r="F179">
-        <v>517</v>
+        <v>277</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -17594,7 +17594,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>598</v>
+        <v>482</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -17614,7 +17614,7 @@
         <v>10</v>
       </c>
       <c r="F181">
-        <v>934</v>
+        <v>418</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -17634,7 +17634,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>673</v>
+        <v>243</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -17654,7 +17654,7 @@
         <v>10</v>
       </c>
       <c r="F183">
-        <v>831</v>
+        <v>221</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -17674,7 +17674,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>785</v>
+        <v>758</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -17694,7 +17694,7 @@
         <v>10</v>
       </c>
       <c r="F185">
-        <v>766</v>
+        <v>745</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -17714,7 +17714,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>479</v>
+        <v>662</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -17734,7 +17734,7 @@
         <v>10</v>
       </c>
       <c r="F187">
-        <v>979</v>
+        <v>653</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -17754,7 +17754,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>421</v>
+        <v>657</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -17774,7 +17774,7 @@
         <v>10</v>
       </c>
       <c r="F189">
-        <v>472</v>
+        <v>696</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -17794,7 +17794,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>351</v>
+        <v>206</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -17814,7 +17814,7 @@
         <v>10</v>
       </c>
       <c r="F191">
-        <v>482</v>
+        <v>579</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -17834,7 +17834,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>607</v>
+        <v>559</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -17854,7 +17854,7 @@
         <v>10</v>
       </c>
       <c r="F193">
-        <v>630</v>
+        <v>777</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -17874,7 +17874,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>639</v>
+        <v>538</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -17894,7 +17894,7 @@
         <v>10</v>
       </c>
       <c r="F195">
-        <v>535</v>
+        <v>669</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -17914,7 +17914,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -17934,7 +17934,7 @@
         <v>10</v>
       </c>
       <c r="F197">
-        <v>648</v>
+        <v>666</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -17954,7 +17954,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>923</v>
+        <v>539</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -17974,7 +17974,7 @@
         <v>10</v>
       </c>
       <c r="F199">
-        <v>771</v>
+        <v>610</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -17994,7 +17994,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>651</v>
+        <v>959</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -18014,7 +18014,7 @@
         <v>10</v>
       </c>
       <c r="F201">
-        <v>833</v>
+        <v>219</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -18034,7 +18034,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>916</v>
+        <v>663</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -18054,7 +18054,7 @@
         <v>10</v>
       </c>
       <c r="F203">
-        <v>713</v>
+        <v>295</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -18074,7 +18074,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>463</v>
+        <v>730</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -18094,7 +18094,7 @@
         <v>10</v>
       </c>
       <c r="F205">
-        <v>650</v>
+        <v>951</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
@@ -18114,7 +18114,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>376</v>
+        <v>436</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
@@ -18134,7 +18134,7 @@
         <v>10</v>
       </c>
       <c r="F207">
-        <v>753</v>
+        <v>904</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -18154,7 +18154,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>801</v>
+        <v>833</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -18174,7 +18174,7 @@
         <v>10</v>
       </c>
       <c r="F209">
-        <v>674</v>
+        <v>889</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -18194,7 +18194,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>864</v>
+        <v>401</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -18214,7 +18214,7 @@
         <v>10</v>
       </c>
       <c r="F211">
-        <v>900</v>
+        <v>716</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -18234,7 +18234,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>447</v>
+        <v>484</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -18254,7 +18254,7 @@
         <v>10</v>
       </c>
       <c r="F213">
-        <v>595</v>
+        <v>325</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -18274,7 +18274,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>654</v>
+        <v>862</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -18294,7 +18294,7 @@
         <v>10</v>
       </c>
       <c r="F215">
-        <v>334</v>
+        <v>992</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -18314,7 +18314,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>913</v>
+        <v>835</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -18334,7 +18334,7 @@
         <v>10</v>
       </c>
       <c r="F217">
-        <v>483</v>
+        <v>876</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -18354,7 +18354,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>805</v>
+        <v>471</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -18374,7 +18374,7 @@
         <v>10</v>
       </c>
       <c r="F219">
-        <v>341</v>
+        <v>729</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -18394,7 +18394,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>354</v>
+        <v>297</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -18414,7 +18414,7 @@
         <v>10</v>
       </c>
       <c r="F221">
-        <v>780</v>
+        <v>510</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -18434,7 +18434,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>802</v>
+        <v>512</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -18454,7 +18454,7 @@
         <v>10</v>
       </c>
       <c r="F223">
-        <v>201</v>
+        <v>267</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -18474,7 +18474,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>658</v>
+        <v>979</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -18494,7 +18494,7 @@
         <v>10</v>
       </c>
       <c r="F225">
-        <v>264</v>
+        <v>951</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -18514,7 +18514,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>834</v>
+        <v>396</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -18534,7 +18534,7 @@
         <v>10</v>
       </c>
       <c r="F227">
-        <v>881</v>
+        <v>858</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
@@ -18554,7 +18554,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>475</v>
+        <v>239</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -18574,7 +18574,7 @@
         <v>10</v>
       </c>
       <c r="F229">
-        <v>467</v>
+        <v>379</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -18594,7 +18594,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>630</v>
+        <v>541</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -18614,7 +18614,7 @@
         <v>10</v>
       </c>
       <c r="F231">
-        <v>696</v>
+        <v>370</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -18634,7 +18634,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>296</v>
+        <v>938</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -18654,7 +18654,7 @@
         <v>10</v>
       </c>
       <c r="F233">
-        <v>677</v>
+        <v>801</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -18674,7 +18674,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>933</v>
+        <v>583</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -18694,7 +18694,7 @@
         <v>10</v>
       </c>
       <c r="F235">
-        <v>827</v>
+        <v>452</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -18714,7 +18714,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>753</v>
+        <v>943</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -18734,7 +18734,7 @@
         <v>10</v>
       </c>
       <c r="F237">
-        <v>531</v>
+        <v>289</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -18754,7 +18754,7 @@
         <v>10</v>
       </c>
       <c r="F238">
-        <v>311</v>
+        <v>390</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -18774,7 +18774,7 @@
         <v>10</v>
       </c>
       <c r="F239">
-        <v>264</v>
+        <v>963</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -18794,7 +18794,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>485</v>
+        <v>930</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -18814,7 +18814,7 @@
         <v>10</v>
       </c>
       <c r="F241">
-        <v>915</v>
+        <v>904</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -18834,7 +18834,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>228</v>
+        <v>783</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -18854,7 +18854,7 @@
         <v>10</v>
       </c>
       <c r="F243">
-        <v>299</v>
+        <v>362</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -18874,7 +18874,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>593</v>
+        <v>659</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -18894,7 +18894,7 @@
         <v>10</v>
       </c>
       <c r="F245">
-        <v>480</v>
+        <v>612</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -18914,7 +18914,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>462</v>
+        <v>851</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -18934,7 +18934,7 @@
         <v>10</v>
       </c>
       <c r="F247">
-        <v>590</v>
+        <v>355</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -18954,7 +18954,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>381</v>
+        <v>868</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -18974,7 +18974,7 @@
         <v>10</v>
       </c>
       <c r="F249">
-        <v>946</v>
+        <v>837</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -18994,7 +18994,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>712</v>
+        <v>386</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -19014,7 +19014,7 @@
         <v>10</v>
       </c>
       <c r="F251">
-        <v>713</v>
+        <v>337</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -19034,7 +19034,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>450</v>
+        <v>676</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -19054,7 +19054,7 @@
         <v>10</v>
       </c>
       <c r="F253">
-        <v>981</v>
+        <v>464</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -19074,7 +19074,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>856</v>
+        <v>938</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -19094,7 +19094,7 @@
         <v>10</v>
       </c>
       <c r="F255">
-        <v>837</v>
+        <v>658</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -19114,7 +19114,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>694</v>
+        <v>397</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -19134,7 +19134,7 @@
         <v>10</v>
       </c>
       <c r="F257">
-        <v>690</v>
+        <v>358</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -19154,7 +19154,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>540</v>
+        <v>377</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
@@ -19174,7 +19174,7 @@
         <v>10</v>
       </c>
       <c r="F259">
-        <v>740</v>
+        <v>909</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -19194,7 +19194,7 @@
         <v>10</v>
       </c>
       <c r="F260">
-        <v>938</v>
+        <v>502</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -19214,7 +19214,7 @@
         <v>10</v>
       </c>
       <c r="F261">
-        <v>615</v>
+        <v>338</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -19234,7 +19234,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>514</v>
+        <v>958</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
@@ -19254,7 +19254,7 @@
         <v>10</v>
       </c>
       <c r="F263">
-        <v>726</v>
+        <v>645</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -19274,7 +19274,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>474</v>
+        <v>712</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -19294,7 +19294,7 @@
         <v>10</v>
       </c>
       <c r="F265">
-        <v>802</v>
+        <v>701</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -19314,7 +19314,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>825</v>
+        <v>842</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -19334,7 +19334,7 @@
         <v>10</v>
       </c>
       <c r="F267">
-        <v>770</v>
+        <v>800</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -19354,7 +19354,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>314</v>
+        <v>267</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
@@ -19374,7 +19374,7 @@
         <v>10</v>
       </c>
       <c r="F269">
-        <v>676</v>
+        <v>981</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -19394,7 +19394,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>933</v>
+        <v>575</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
@@ -19414,7 +19414,7 @@
         <v>10</v>
       </c>
       <c r="F271">
-        <v>748</v>
+        <v>936</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
@@ -19434,7 +19434,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>324</v>
+        <v>984</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -19454,7 +19454,7 @@
         <v>10</v>
       </c>
       <c r="F273">
-        <v>448</v>
+        <v>943</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
@@ -19474,7 +19474,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>366</v>
+        <v>800</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -19494,7 +19494,7 @@
         <v>10</v>
       </c>
       <c r="F275">
-        <v>283</v>
+        <v>434</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -19514,7 +19514,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>639</v>
+        <v>411</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -19534,7 +19534,7 @@
         <v>10</v>
       </c>
       <c r="F277">
-        <v>957</v>
+        <v>922</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -19554,7 +19554,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>279</v>
+        <v>460</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -19574,7 +19574,7 @@
         <v>10</v>
       </c>
       <c r="F279">
-        <v>465</v>
+        <v>297</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -19594,7 +19594,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>337</v>
+        <v>501</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -19614,7 +19614,7 @@
         <v>10</v>
       </c>
       <c r="F281">
-        <v>506</v>
+        <v>488</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -19634,7 +19634,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>684</v>
+        <v>837</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -19654,7 +19654,7 @@
         <v>10</v>
       </c>
       <c r="F283">
-        <v>453</v>
+        <v>318</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -19674,7 +19674,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>382</v>
+        <v>284</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
@@ -19694,7 +19694,7 @@
         <v>10</v>
       </c>
       <c r="F285">
-        <v>989</v>
+        <v>806</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -19714,7 +19714,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>630</v>
+        <v>319</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -19734,7 +19734,7 @@
         <v>10</v>
       </c>
       <c r="F287">
-        <v>314</v>
+        <v>576</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -19754,7 +19754,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>728</v>
+        <v>656</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -19774,7 +19774,7 @@
         <v>10</v>
       </c>
       <c r="F289">
-        <v>562</v>
+        <v>207</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -19794,7 +19794,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>406</v>
+        <v>233</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -19814,7 +19814,7 @@
         <v>10</v>
       </c>
       <c r="F291">
-        <v>886</v>
+        <v>688</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -19834,7 +19834,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>646</v>
+        <v>296</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -19854,7 +19854,7 @@
         <v>10</v>
       </c>
       <c r="F293">
-        <v>502</v>
+        <v>414</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -19874,7 +19874,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>225</v>
+        <v>704</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -19894,7 +19894,7 @@
         <v>10</v>
       </c>
       <c r="F295">
-        <v>368</v>
+        <v>694</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -19914,7 +19914,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>710</v>
+        <v>378</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -19934,7 +19934,7 @@
         <v>10</v>
       </c>
       <c r="F297">
-        <v>727</v>
+        <v>950</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -19954,7 +19954,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>859</v>
+        <v>902</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -19974,7 +19974,7 @@
         <v>10</v>
       </c>
       <c r="F299">
-        <v>546</v>
+        <v>789</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -19994,7 +19994,7 @@
         <v>10</v>
       </c>
       <c r="F300">
-        <v>209</v>
+        <v>766</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -20014,7 +20014,7 @@
         <v>10</v>
       </c>
       <c r="F301">
-        <v>503</v>
+        <v>971</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -20034,7 +20034,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>727</v>
+        <v>425</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -20054,7 +20054,7 @@
         <v>10</v>
       </c>
       <c r="F303">
-        <v>918</v>
+        <v>900</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -20074,7 +20074,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>434</v>
+        <v>968</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -20094,7 +20094,7 @@
         <v>10</v>
       </c>
       <c r="F305">
-        <v>448</v>
+        <v>470</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -20114,7 +20114,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>955</v>
+        <v>247</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -20134,7 +20134,7 @@
         <v>10</v>
       </c>
       <c r="F307">
-        <v>849</v>
+        <v>986</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -20154,7 +20154,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>741</v>
+        <v>505</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -20174,7 +20174,7 @@
         <v>10</v>
       </c>
       <c r="F309">
-        <v>775</v>
+        <v>749</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
@@ -20194,7 +20194,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>235</v>
+        <v>825</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -20214,7 +20214,7 @@
         <v>10</v>
       </c>
       <c r="F311">
-        <v>244</v>
+        <v>902</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
@@ -20234,7 +20234,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>668</v>
+        <v>732</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -20254,7 +20254,7 @@
         <v>10</v>
       </c>
       <c r="F313">
-        <v>375</v>
+        <v>830</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -20274,7 +20274,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>651</v>
+        <v>606</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -20294,7 +20294,7 @@
         <v>10</v>
       </c>
       <c r="F315">
-        <v>640</v>
+        <v>212</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -20314,7 +20314,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>832</v>
+        <v>961</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -20334,7 +20334,7 @@
         <v>10</v>
       </c>
       <c r="F317">
-        <v>705</v>
+        <v>304</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -20354,7 +20354,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>487</v>
+        <v>854</v>
       </c>
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
@@ -20374,7 +20374,7 @@
         <v>10</v>
       </c>
       <c r="F319">
-        <v>305</v>
+        <v>893</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
@@ -20394,7 +20394,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>219</v>
+        <v>736</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
@@ -20414,7 +20414,7 @@
         <v>10</v>
       </c>
       <c r="F321">
-        <v>428</v>
+        <v>517</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
@@ -20434,7 +20434,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>374</v>
+        <v>794</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
@@ -20454,7 +20454,7 @@
         <v>10</v>
       </c>
       <c r="F323">
-        <v>253</v>
+        <v>319</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -20474,7 +20474,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>220</v>
+        <v>669</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -20494,7 +20494,7 @@
         <v>10</v>
       </c>
       <c r="F325">
-        <v>451</v>
+        <v>611</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -20514,7 +20514,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>574</v>
+        <v>363</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -20534,7 +20534,7 @@
         <v>10</v>
       </c>
       <c r="F327">
-        <v>783</v>
+        <v>238</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -20554,7 +20554,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>343</v>
+        <v>551</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -20574,7 +20574,7 @@
         <v>10</v>
       </c>
       <c r="F329">
-        <v>891</v>
+        <v>410</v>
       </c>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
@@ -20594,7 +20594,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>548</v>
+        <v>872</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -20614,7 +20614,7 @@
         <v>10</v>
       </c>
       <c r="F331">
-        <v>688</v>
+        <v>383</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -20634,7 +20634,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>676</v>
+        <v>362</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -20654,7 +20654,7 @@
         <v>10</v>
       </c>
       <c r="F333">
-        <v>220</v>
+        <v>374</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -20674,7 +20674,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -20694,7 +20694,7 @@
         <v>10</v>
       </c>
       <c r="F335">
-        <v>867</v>
+        <v>305</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
@@ -20714,7 +20714,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>935</v>
+        <v>670</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -20734,7 +20734,7 @@
         <v>10</v>
       </c>
       <c r="F337">
-        <v>595</v>
+        <v>611</v>
       </c>
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
@@ -20754,7 +20754,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>923</v>
+        <v>734</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -20774,7 +20774,7 @@
         <v>10</v>
       </c>
       <c r="F339">
-        <v>956</v>
+        <v>300</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
@@ -20794,7 +20794,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>316</v>
+        <v>413</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -20814,7 +20814,7 @@
         <v>10</v>
       </c>
       <c r="F341">
-        <v>529</v>
+        <v>519</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -20834,7 +20834,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>631</v>
+        <v>260</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -20854,7 +20854,7 @@
         <v>10</v>
       </c>
       <c r="F343">
-        <v>946</v>
+        <v>922</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -20874,7 +20874,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -20894,7 +20894,7 @@
         <v>10</v>
       </c>
       <c r="F345">
-        <v>692</v>
+        <v>832</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -20914,7 +20914,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>802</v>
+        <v>652</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -20934,7 +20934,7 @@
         <v>10</v>
       </c>
       <c r="F347">
-        <v>454</v>
+        <v>414</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -20954,7 +20954,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>679</v>
+        <v>977</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -20974,7 +20974,7 @@
         <v>10</v>
       </c>
       <c r="F349">
-        <v>233</v>
+        <v>845</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -20994,7 +20994,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>814</v>
+        <v>430</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -21014,7 +21014,7 @@
         <v>10</v>
       </c>
       <c r="F351">
-        <v>799</v>
+        <v>227</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -21034,7 +21034,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>511</v>
+        <v>746</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -21054,7 +21054,7 @@
         <v>10</v>
       </c>
       <c r="F353">
-        <v>977</v>
+        <v>910</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -21074,7 +21074,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>521</v>
+        <v>416</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -21094,7 +21094,7 @@
         <v>10</v>
       </c>
       <c r="F355">
-        <v>827</v>
+        <v>757</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -21114,7 +21114,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>310</v>
+        <v>270</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -21134,7 +21134,7 @@
         <v>10</v>
       </c>
       <c r="F357">
-        <v>452</v>
+        <v>586</v>
       </c>
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
@@ -21154,7 +21154,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>667</v>
+        <v>583</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
@@ -21174,7 +21174,7 @@
         <v>10</v>
       </c>
       <c r="F359">
-        <v>500</v>
+        <v>545</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -21194,7 +21194,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>213</v>
+        <v>618</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -21214,7 +21214,7 @@
         <v>10</v>
       </c>
       <c r="F361">
-        <v>735</v>
+        <v>294</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -21234,7 +21234,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>816</v>
+        <v>563</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -21254,7 +21254,7 @@
         <v>10</v>
       </c>
       <c r="F363">
-        <v>453</v>
+        <v>420</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -21274,7 +21274,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>907</v>
+        <v>688</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -21294,7 +21294,7 @@
         <v>10</v>
       </c>
       <c r="F365">
-        <v>844</v>
+        <v>453</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -21314,7 +21314,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -21334,7 +21334,7 @@
         <v>10</v>
       </c>
       <c r="F367">
-        <v>317</v>
+        <v>236</v>
       </c>
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
@@ -21354,7 +21354,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>731</v>
+        <v>830</v>
       </c>
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
@@ -21374,7 +21374,7 @@
         <v>10</v>
       </c>
       <c r="F369">
-        <v>613</v>
+        <v>648</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -21394,7 +21394,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>743</v>
+        <v>720</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -21414,7 +21414,7 @@
         <v>10</v>
       </c>
       <c r="F371">
-        <v>456</v>
+        <v>374</v>
       </c>
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
@@ -21434,7 +21434,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>915</v>
+        <v>633</v>
       </c>
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
@@ -21454,7 +21454,7 @@
         <v>10</v>
       </c>
       <c r="F373">
-        <v>741</v>
+        <v>252</v>
       </c>
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
@@ -21474,7 +21474,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>226</v>
+        <v>922</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -21494,7 +21494,7 @@
         <v>10</v>
       </c>
       <c r="F375">
-        <v>689</v>
+        <v>605</v>
       </c>
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
@@ -21514,7 +21514,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>894</v>
+        <v>473</v>
       </c>
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
@@ -21534,7 +21534,7 @@
         <v>10</v>
       </c>
       <c r="F377">
-        <v>263</v>
+        <v>415</v>
       </c>
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
@@ -21554,7 +21554,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>834</v>
+        <v>251</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -21574,7 +21574,7 @@
         <v>10</v>
       </c>
       <c r="F379">
-        <v>397</v>
+        <v>951</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -21594,7 +21594,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>347</v>
+        <v>946</v>
       </c>
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
@@ -21614,7 +21614,7 @@
         <v>10</v>
       </c>
       <c r="F381">
-        <v>506</v>
+        <v>820</v>
       </c>
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
@@ -21634,7 +21634,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>498</v>
+        <v>985</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -21654,7 +21654,7 @@
         <v>10</v>
       </c>
       <c r="F383">
-        <v>375</v>
+        <v>795</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -21674,7 +21674,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>224</v>
+        <v>449</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -21694,7 +21694,7 @@
         <v>10</v>
       </c>
       <c r="F385">
-        <v>786</v>
+        <v>452</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -21714,7 +21714,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>295</v>
+        <v>624</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -21734,7 +21734,7 @@
         <v>10</v>
       </c>
       <c r="F387">
-        <v>952</v>
+        <v>475</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -21754,7 +21754,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>443</v>
+        <v>407</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -21774,7 +21774,7 @@
         <v>10</v>
       </c>
       <c r="F389">
-        <v>455</v>
+        <v>609</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -21794,7 +21794,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>305</v>
+        <v>832</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -21814,7 +21814,7 @@
         <v>10</v>
       </c>
       <c r="F391">
-        <v>476</v>
+        <v>924</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -21834,7 +21834,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>609</v>
+        <v>464</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -21854,7 +21854,7 @@
         <v>10</v>
       </c>
       <c r="F393">
-        <v>873</v>
+        <v>538</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
@@ -21874,7 +21874,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>605</v>
+        <v>466</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -21894,7 +21894,7 @@
         <v>10</v>
       </c>
       <c r="F395">
-        <v>845</v>
+        <v>257</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -21914,7 +21914,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>722</v>
+        <v>652</v>
       </c>
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
@@ -21934,7 +21934,7 @@
         <v>10</v>
       </c>
       <c r="F397">
-        <v>574</v>
+        <v>426</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
@@ -21954,7 +21954,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>705</v>
+        <v>671</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -21974,7 +21974,7 @@
         <v>10</v>
       </c>
       <c r="F399">
-        <v>962</v>
+        <v>414</v>
       </c>
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
@@ -21994,7 +21994,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>971</v>
+        <v>312</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -22014,7 +22014,7 @@
         <v>10</v>
       </c>
       <c r="F401">
-        <v>276</v>
+        <v>658</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
@@ -22034,7 +22034,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>932</v>
+        <v>340</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -22054,7 +22054,7 @@
         <v>10</v>
       </c>
       <c r="F403">
-        <v>589</v>
+        <v>879</v>
       </c>
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
@@ -22074,7 +22074,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>201</v>
+        <v>365</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -22094,7 +22094,7 @@
         <v>10</v>
       </c>
       <c r="F405">
-        <v>829</v>
+        <v>909</v>
       </c>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -22114,7 +22114,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>425</v>
+        <v>804</v>
       </c>
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
@@ -22134,7 +22134,7 @@
         <v>10</v>
       </c>
       <c r="F407">
-        <v>721</v>
+        <v>966</v>
       </c>
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
@@ -22154,7 +22154,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>490</v>
+        <v>962</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -22174,7 +22174,7 @@
         <v>10</v>
       </c>
       <c r="F409">
-        <v>810</v>
+        <v>254</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
@@ -22194,7 +22194,7 @@
         <v>10</v>
       </c>
       <c r="F410">
-        <v>706</v>
+        <v>291</v>
       </c>
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
@@ -22214,7 +22214,7 @@
         <v>10</v>
       </c>
       <c r="F411">
-        <v>682</v>
+        <v>584</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -22234,7 +22234,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>731</v>
+        <v>460</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -22254,7 +22254,7 @@
         <v>10</v>
       </c>
       <c r="F413">
-        <v>575</v>
+        <v>231</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
@@ -22274,7 +22274,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>519</v>
+        <v>608</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -22294,7 +22294,7 @@
         <v>10</v>
       </c>
       <c r="F415">
-        <v>223</v>
+        <v>421</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -22314,7 +22314,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>890</v>
+        <v>906</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -22334,7 +22334,7 @@
         <v>10</v>
       </c>
       <c r="F417">
-        <v>699</v>
+        <v>399</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -22354,7 +22354,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>853</v>
+        <v>896</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -22374,7 +22374,7 @@
         <v>10</v>
       </c>
       <c r="F419">
-        <v>430</v>
+        <v>245</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -22394,7 +22394,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>600</v>
+        <v>733</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -22414,7 +22414,7 @@
         <v>10</v>
       </c>
       <c r="F421">
-        <v>475</v>
+        <v>917</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -22434,7 +22434,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>553</v>
+        <v>819</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -22454,7 +22454,7 @@
         <v>10</v>
       </c>
       <c r="F423">
-        <v>426</v>
+        <v>400</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -22474,7 +22474,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>999</v>
+        <v>812</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -22494,7 +22494,7 @@
         <v>10</v>
       </c>
       <c r="F425">
-        <v>977</v>
+        <v>410</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -22514,7 +22514,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>355</v>
+        <v>336</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -22534,7 +22534,7 @@
         <v>10</v>
       </c>
       <c r="F427">
-        <v>552</v>
+        <v>859</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
@@ -22554,7 +22554,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>732</v>
+        <v>467</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -22574,7 +22574,7 @@
         <v>10</v>
       </c>
       <c r="F429">
-        <v>862</v>
+        <v>234</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -22594,7 +22594,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>362</v>
+        <v>432</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -22614,7 +22614,7 @@
         <v>10</v>
       </c>
       <c r="F431">
-        <v>527</v>
+        <v>872</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -22634,7 +22634,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>988</v>
+        <v>252</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -22654,7 +22654,7 @@
         <v>10</v>
       </c>
       <c r="F433">
-        <v>530</v>
+        <v>898</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -22674,7 +22674,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>395</v>
+        <v>694</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -22694,7 +22694,7 @@
         <v>10</v>
       </c>
       <c r="F435">
-        <v>440</v>
+        <v>639</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -22714,7 +22714,7 @@
         <v>10</v>
       </c>
       <c r="F436">
-        <v>469</v>
+        <v>521</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -22734,7 +22734,7 @@
         <v>10</v>
       </c>
       <c r="F437">
-        <v>368</v>
+        <v>917</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -22754,7 +22754,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>747</v>
+        <v>718</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -22774,7 +22774,7 @@
         <v>10</v>
       </c>
       <c r="F439">
-        <v>776</v>
+        <v>654</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
@@ -22794,7 +22794,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>476</v>
+        <v>719</v>
       </c>
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
@@ -22814,7 +22814,7 @@
         <v>10</v>
       </c>
       <c r="F441">
-        <v>250</v>
+        <v>465</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -22834,7 +22834,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>327</v>
+        <v>937</v>
       </c>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
@@ -22854,7 +22854,7 @@
         <v>10</v>
       </c>
       <c r="F443">
-        <v>589</v>
+        <v>688</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -22894,7 +22894,7 @@
         <v>10</v>
       </c>
       <c r="F445">
-        <v>636</v>
+        <v>562</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -22914,7 +22914,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>477</v>
+        <v>225</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -22934,7 +22934,7 @@
         <v>10</v>
       </c>
       <c r="F447">
-        <v>486</v>
+        <v>981</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -22954,7 +22954,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>739</v>
+        <v>758</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -22974,7 +22974,7 @@
         <v>10</v>
       </c>
       <c r="F449">
-        <v>924</v>
+        <v>843</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -22994,7 +22994,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>346</v>
+        <v>902</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -23014,7 +23014,7 @@
         <v>10</v>
       </c>
       <c r="F451">
-        <v>528</v>
+        <v>445</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -23034,7 +23034,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>206</v>
+        <v>638</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -23054,7 +23054,7 @@
         <v>10</v>
       </c>
       <c r="F453">
-        <v>649</v>
+        <v>763</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -23074,7 +23074,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>245</v>
+        <v>561</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -23094,7 +23094,7 @@
         <v>10</v>
       </c>
       <c r="F455">
-        <v>610</v>
+        <v>989</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -23114,7 +23114,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>229</v>
+        <v>912</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -23134,7 +23134,7 @@
         <v>10</v>
       </c>
       <c r="F457">
-        <v>531</v>
+        <v>418</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
@@ -23154,7 +23154,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>316</v>
+        <v>676</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -23174,7 +23174,7 @@
         <v>10</v>
       </c>
       <c r="F459">
-        <v>784</v>
+        <v>608</v>
       </c>
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
@@ -23194,7 +23194,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>956</v>
+        <v>633</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -23214,7 +23214,7 @@
         <v>10</v>
       </c>
       <c r="F461">
-        <v>203</v>
+        <v>220</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -23234,7 +23234,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>347</v>
+        <v>288</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -23254,7 +23254,7 @@
         <v>10</v>
       </c>
       <c r="F463">
-        <v>963</v>
+        <v>589</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -23274,7 +23274,7 @@
         <v>10</v>
       </c>
       <c r="F464">
-        <v>579</v>
+        <v>431</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -23294,7 +23294,7 @@
         <v>10</v>
       </c>
       <c r="F465">
-        <v>362</v>
+        <v>309</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -23314,7 +23314,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>652</v>
+        <v>589</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
@@ -23334,7 +23334,7 @@
         <v>10</v>
       </c>
       <c r="F467">
-        <v>357</v>
+        <v>637</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -23354,7 +23354,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>895</v>
+        <v>786</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -23374,7 +23374,7 @@
         <v>10</v>
       </c>
       <c r="F469">
-        <v>327</v>
+        <v>827</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -23394,7 +23394,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>750</v>
+        <v>510</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -23414,7 +23414,7 @@
         <v>10</v>
       </c>
       <c r="F471">
-        <v>984</v>
+        <v>743</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -23434,7 +23434,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>994</v>
+        <v>666</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
@@ -23454,7 +23454,7 @@
         <v>10</v>
       </c>
       <c r="F473">
-        <v>535</v>
+        <v>723</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -23474,7 +23474,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>379</v>
+        <v>857</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -23494,7 +23494,7 @@
         <v>10</v>
       </c>
       <c r="F475">
-        <v>995</v>
+        <v>454</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -23514,7 +23514,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>926</v>
+        <v>879</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -23534,7 +23534,7 @@
         <v>10</v>
       </c>
       <c r="F477">
-        <v>942</v>
+        <v>257</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -23554,7 +23554,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>291</v>
+        <v>780</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
@@ -23574,7 +23574,7 @@
         <v>10</v>
       </c>
       <c r="F479">
-        <v>220</v>
+        <v>726</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
@@ -23594,7 +23594,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>851</v>
+        <v>698</v>
       </c>
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
@@ -23614,7 +23614,7 @@
         <v>10</v>
       </c>
       <c r="F481">
-        <v>330</v>
+        <v>880</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
@@ -23634,7 +23634,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>962</v>
+        <v>913</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
@@ -23654,7 +23654,7 @@
         <v>10</v>
       </c>
       <c r="F483">
-        <v>202</v>
+        <v>852</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
@@ -23674,7 +23674,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>208</v>
+        <v>945</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -23694,7 +23694,7 @@
         <v>10</v>
       </c>
       <c r="F485">
-        <v>924</v>
+        <v>270</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
@@ -23714,7 +23714,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>544</v>
+        <v>279</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
@@ -23734,7 +23734,7 @@
         <v>10</v>
       </c>
       <c r="F487">
-        <v>491</v>
+        <v>885</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -23754,7 +23754,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>473</v>
+        <v>374</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
@@ -23774,7 +23774,7 @@
         <v>10</v>
       </c>
       <c r="F489">
-        <v>804</v>
+        <v>782</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -23794,7 +23794,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>873</v>
+        <v>219</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -23814,7 +23814,7 @@
         <v>10</v>
       </c>
       <c r="F491">
-        <v>379</v>
+        <v>417</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
@@ -23834,7 +23834,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>456</v>
+        <v>586</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -23854,7 +23854,7 @@
         <v>10</v>
       </c>
       <c r="F493">
-        <v>257</v>
+        <v>200</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -23874,7 +23874,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>584</v>
+        <v>855</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -23894,7 +23894,7 @@
         <v>10</v>
       </c>
       <c r="F495">
-        <v>451</v>
+        <v>745</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -23914,7 +23914,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>399</v>
+        <v>767</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -23934,7 +23934,7 @@
         <v>10</v>
       </c>
       <c r="F497">
-        <v>456</v>
+        <v>530</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
@@ -23954,7 +23954,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>305</v>
+        <v>553</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -23974,7 +23974,7 @@
         <v>10</v>
       </c>
       <c r="F499">
-        <v>217</v>
+        <v>442</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -23994,7 +23994,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>311</v>
+        <v>200</v>
       </c>
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
@@ -24014,7 +24014,7 @@
         <v>10</v>
       </c>
       <c r="F501">
-        <v>447</v>
+        <v>757</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
@@ -24034,7 +24034,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>924</v>
+        <v>893</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -24054,7 +24054,7 @@
         <v>10</v>
       </c>
       <c r="F503">
-        <v>342</v>
+        <v>997</v>
       </c>
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
@@ -24074,7 +24074,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>865</v>
+        <v>426</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -24094,7 +24094,7 @@
         <v>10</v>
       </c>
       <c r="F505">
-        <v>803</v>
+        <v>993</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -24114,7 +24114,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>759</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -24264,7 +24264,7 @@
         <v>622</v>
       </c>
       <c r="F2">
-        <v>333</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -24284,7 +24284,7 @@
         <v>622</v>
       </c>
       <c r="F3">
-        <v>557</v>
+        <v>958</v>
       </c>
     </row>
   </sheetData>
